--- a/JAZZ.xlsx
+++ b/JAZZ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC968596-C0FA-4AE2-81E5-35ED7935D345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F1113D-21BD-4AE6-8983-D69FD0DAFD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16150" yWindow="1920" windowWidth="21870" windowHeight="14480" xr2:uid="{79B0AABE-526A-4476-AFB2-442F9E053778}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="21200" windowHeight="16100" xr2:uid="{79B0AABE-526A-4476-AFB2-442F9E053778}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>tc={C34C856B-F6CC-4EC0-B6F9-FB303B5D0A64}</author>
   </authors>
   <commentList>
-    <comment ref="AJ16" authorId="0" shapeId="0" xr:uid="{08384C6B-BC0B-D540-9CAB-67A68D6812B6}">
+    <comment ref="AO16" authorId="0" shapeId="0" xr:uid="{08384C6B-BC0B-D540-9CAB-67A68D6812B6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -52,7 +52,7 @@
     Q2 guidance: 4000-4100</t>
       </text>
     </comment>
-    <comment ref="AK16" authorId="1" shapeId="0" xr:uid="{C34C856B-F6CC-4EC0-B6F9-FB303B5D0A64}">
+    <comment ref="AP16" authorId="1" shapeId="0" xr:uid="{C34C856B-F6CC-4EC0-B6F9-FB303B5D0A64}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="148">
   <si>
     <t>Price</t>
   </si>
@@ -495,6 +495,21 @@
   </si>
   <si>
     <t>L+SE</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Modeyso (dordaviprone)</t>
   </si>
 </sst>
 </file>
@@ -505,7 +520,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -526,12 +541,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -541,7 +550,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -635,12 +644,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -683,10 +723,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -761,13 +808,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
+      <xdr:col>41</xdr:col>
       <xdr:colOff>23389</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
+      <xdr:col>41</xdr:col>
       <xdr:colOff>23389</xdr:colOff>
       <xdr:row>57</xdr:row>
       <xdr:rowOff>86406</xdr:rowOff>
@@ -1115,10 +1162,10 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="AJ16" dT="2024-09-06T17:58:56.69" personId="{4D2BE095-5078-834E-8E0F-68F9D6A31E87}" id="{08384C6B-BC0B-D540-9CAB-67A68D6812B6}">
+  <threadedComment ref="AO16" dT="2024-09-06T17:58:56.69" personId="{4D2BE095-5078-834E-8E0F-68F9D6A31E87}" id="{08384C6B-BC0B-D540-9CAB-67A68D6812B6}">
     <text>Q2 guidance: 4000-4100</text>
   </threadedComment>
-  <threadedComment ref="AK16" dT="2025-05-19T15:09:05.61" personId="{4D2BE095-5078-834E-8E0F-68F9D6A31E87}" id="{C34C856B-F6CC-4EC0-B6F9-FB303B5D0A64}">
+  <threadedComment ref="AP16" dT="2025-05-19T15:09:05.61" personId="{4D2BE095-5078-834E-8E0F-68F9D6A31E87}" id="{C34C856B-F6CC-4EC0-B6F9-FB303B5D0A64}">
     <text>5/6/25 guidance: 4.150-4.400B
 2/25/25 guidance: 4.150-4.400B</text>
   </threadedComment>
@@ -1127,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{601CF0EA-6190-476D-832E-2260D789DF8A}">
-  <dimension ref="B2:L14"/>
+  <dimension ref="B2:L15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -1161,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="20">
-        <v>107.91</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
@@ -1181,10 +1228,10 @@
         <v>1</v>
       </c>
       <c r="K3" s="1">
-        <v>61.632840999999999</v>
+        <v>61.9</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
@@ -1205,7 +1252,7 @@
       </c>
       <c r="K4" s="1">
         <f>+K2*K3</f>
-        <v>6650.79987231</v>
+        <v>15784.5</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
@@ -1223,11 +1270,10 @@
         <v>3</v>
       </c>
       <c r="K5" s="1">
-        <f>1861.946+710</f>
-        <v>2571.9459999999999</v>
+        <v>2900</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
@@ -1245,11 +1291,10 @@
         <v>4</v>
       </c>
       <c r="K6" s="1">
-        <f>5336.481+31</f>
-        <v>5367.4809999999998</v>
+        <v>5400</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
@@ -1274,105 +1319,118 @@
       </c>
       <c r="K7" s="1">
         <f>+K4-K5+K6</f>
-        <v>9446.3348723099989</v>
+        <v>18284.5</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="22">
-        <v>43371</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="15"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="11"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21" t="s">
+      <c r="B9" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="22">
+        <v>43371</v>
+      </c>
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="11"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="14" t="s">
+      <c r="G10" s="12"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23" t="s">
+      <c r="C11" s="28"/>
+      <c r="D11" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23" t="s">
+      <c r="E11" s="28"/>
+      <c r="F11" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="H11" s="15"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="30"/>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23" t="s">
-        <v>66</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="15"/>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C14" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="23" t="s">
+      <c r="D14" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="18"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="15"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="16"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="18"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1382,21 +1440,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BF25E3F-0D5A-4F1A-A75A-A8CE578AC72F}">
-  <dimension ref="A1:DF58"/>
+  <dimension ref="A1:DK58"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
     <col min="3" max="16" width="9.1796875" style="2"/>
-    <col min="50" max="50" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="11.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1469,83 +1527,96 @@
       <c r="Z2" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="AB2">
+      <c r="AA2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AC2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AE2" s="2"/>
+      <c r="AG2">
         <v>2016</v>
       </c>
-      <c r="AC2">
+      <c r="AH2">
         <v>2017</v>
       </c>
-      <c r="AD2">
+      <c r="AI2">
         <v>2018</v>
       </c>
-      <c r="AE2">
+      <c r="AJ2">
         <v>2019</v>
       </c>
-      <c r="AF2">
+      <c r="AK2">
         <v>2020</v>
       </c>
-      <c r="AG2">
-        <f>+AF2+1</f>
+      <c r="AL2">
+        <f>+AK2+1</f>
         <v>2021</v>
       </c>
-      <c r="AH2">
-        <f t="shared" ref="AH2:AU2" si="0">+AG2+1</f>
+      <c r="AM2">
+        <f t="shared" ref="AM2:AZ2" si="0">+AL2+1</f>
         <v>2022</v>
       </c>
-      <c r="AI2">
+      <c r="AN2">
         <f t="shared" si="0"/>
         <v>2023</v>
       </c>
-      <c r="AJ2">
+      <c r="AO2">
         <f t="shared" si="0"/>
         <v>2024</v>
       </c>
-      <c r="AK2">
+      <c r="AP2">
         <f t="shared" si="0"/>
         <v>2025</v>
       </c>
-      <c r="AL2">
+      <c r="AQ2">
         <f t="shared" si="0"/>
         <v>2026</v>
       </c>
-      <c r="AM2">
+      <c r="AR2">
         <f t="shared" si="0"/>
         <v>2027</v>
       </c>
-      <c r="AN2">
+      <c r="AS2">
         <f t="shared" si="0"/>
         <v>2028</v>
       </c>
-      <c r="AO2">
+      <c r="AT2">
         <f t="shared" si="0"/>
         <v>2029</v>
       </c>
-      <c r="AP2">
+      <c r="AU2">
         <f t="shared" si="0"/>
         <v>2030</v>
       </c>
-      <c r="AQ2">
+      <c r="AV2">
         <f t="shared" si="0"/>
         <v>2031</v>
       </c>
-      <c r="AR2">
+      <c r="AW2">
         <f t="shared" si="0"/>
         <v>2032</v>
       </c>
-      <c r="AS2">
+      <c r="AX2">
         <f t="shared" si="0"/>
         <v>2033</v>
       </c>
-      <c r="AT2">
+      <c r="AY2">
         <f t="shared" si="0"/>
         <v>2034</v>
       </c>
-      <c r="AU2">
+      <c r="AZ2">
         <f t="shared" si="0"/>
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
@@ -1619,77 +1690,84 @@
         <f>+Y3-1</f>
         <v>34.241</v>
       </c>
-      <c r="AD3" s="3">
+      <c r="AA3" s="4">
+        <v>31.2</v>
+      </c>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AI3" s="3">
         <v>1404.866</v>
       </c>
-      <c r="AE3" s="3">
+      <c r="AJ3" s="3">
         <v>1642.5250000000001</v>
       </c>
-      <c r="AF3" s="3">
+      <c r="AK3" s="3">
         <v>1741.758</v>
       </c>
-      <c r="AG3" s="3">
+      <c r="AL3" s="3">
         <f>SUM(G3:J3)</f>
         <v>1265.83</v>
       </c>
-      <c r="AH3" s="3">
-        <f t="shared" ref="AH3:AH8" si="1">SUM(K3:N3)</f>
+      <c r="AM3" s="3">
+        <f t="shared" ref="AM3:AM8" si="1">SUM(K3:N3)</f>
         <v>1020.453</v>
       </c>
-      <c r="AI3" s="3">
+      <c r="AN3" s="3">
         <f>SUM(O3:R3)</f>
         <v>569.73</v>
       </c>
-      <c r="AJ3" s="3">
-        <f>SUM(S3:V3)</f>
+      <c r="AO3" s="3">
+        <f t="shared" ref="AO3:AO10" si="2">SUM(S3:V3)</f>
         <v>236.88200000000001</v>
       </c>
-      <c r="AK3" s="3">
-        <f>SUM(W3:Z3)</f>
+      <c r="AP3" s="3">
+        <f t="shared" ref="AP3:AP15" si="3">SUM(W3:Z3)</f>
         <v>142.964</v>
       </c>
-      <c r="AL3" s="3">
-        <f t="shared" ref="AL3:AT3" si="2">+AK3*0.5</f>
+      <c r="AQ3" s="3">
+        <f t="shared" ref="AQ3:AY3" si="4">+AP3*0.5</f>
         <v>71.481999999999999</v>
       </c>
-      <c r="AM3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AR3" s="3">
+        <f t="shared" si="4"/>
         <v>35.741</v>
       </c>
-      <c r="AN3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AS3" s="3">
+        <f t="shared" si="4"/>
         <v>17.8705</v>
       </c>
-      <c r="AO3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AT3" s="3">
+        <f t="shared" si="4"/>
         <v>8.9352499999999999</v>
       </c>
-      <c r="AP3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AU3" s="3">
+        <f t="shared" si="4"/>
         <v>4.467625</v>
       </c>
-      <c r="AQ3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AV3" s="3">
+        <f t="shared" si="4"/>
         <v>2.2338125</v>
       </c>
-      <c r="AR3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AW3" s="3">
+        <f t="shared" si="4"/>
         <v>1.11690625</v>
       </c>
-      <c r="AS3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AX3" s="3">
+        <f t="shared" si="4"/>
         <v>0.55845312499999999</v>
       </c>
-      <c r="AT3" s="3">
-        <f t="shared" si="2"/>
+      <c r="AY3" s="3">
+        <f t="shared" si="4"/>
         <v>0.2792265625</v>
       </c>
-      <c r="AU3" s="3">
-        <f t="shared" ref="AU3" si="3">+AT3*0.5</f>
+      <c r="AZ3" s="3">
+        <f t="shared" ref="AZ3" si="5">+AY3*0.5</f>
         <v>0.13961328125</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
@@ -1752,88 +1830,95 @@
         <v>344.80399999999997</v>
       </c>
       <c r="X4" s="4">
-        <f>+T4*1.07</f>
+        <f t="shared" ref="X4:Z5" si="6">+T4*1.07</f>
         <v>394.26504</v>
       </c>
       <c r="Y4" s="4">
-        <f>+U4*1.07</f>
+        <f t="shared" si="6"/>
         <v>390.33204100000006</v>
       </c>
       <c r="Z4" s="4">
-        <f>+V4*1.07</f>
+        <f t="shared" si="6"/>
         <v>429.03148000000004</v>
       </c>
-      <c r="AD4" s="3">
+      <c r="AA4" s="4">
+        <v>408</v>
+      </c>
+      <c r="AB4" s="4"/>
+      <c r="AC4" s="4"/>
+      <c r="AD4" s="4"/>
+      <c r="AE4" s="4"/>
+      <c r="AI4" s="3">
         <v>0</v>
       </c>
-      <c r="AE4" s="3">
+      <c r="AJ4" s="3">
         <v>0</v>
       </c>
-      <c r="AF4" s="3">
+      <c r="AK4" s="3">
         <v>15.263999999999999</v>
       </c>
-      <c r="AG4" s="3">
-        <f t="shared" ref="AG4:AG20" si="4">SUM(G4:J4)</f>
+      <c r="AL4" s="3">
+        <f t="shared" ref="AL4:AL20" si="7">SUM(G4:J4)</f>
         <v>535.29700000000003</v>
       </c>
-      <c r="AH4" s="3">
+      <c r="AM4" s="3">
         <f t="shared" si="1"/>
         <v>958.42500000000007</v>
       </c>
-      <c r="AI4" s="3">
-        <f t="shared" ref="AI4:AI19" si="5">SUM(O4:R4)</f>
+      <c r="AN4" s="3">
+        <f t="shared" ref="AN4:AN19" si="8">SUM(O4:R4)</f>
         <v>1272.9770000000001</v>
       </c>
-      <c r="AJ4" s="3">
-        <f>SUM(S4:V4)</f>
+      <c r="AO4" s="3">
+        <f t="shared" si="2"/>
         <v>1449.5322999999999</v>
       </c>
-      <c r="AK4" s="3">
-        <f>SUM(W4:Z4)</f>
+      <c r="AP4" s="3">
+        <f t="shared" si="3"/>
         <v>1558.4325610000001</v>
       </c>
-      <c r="AL4" s="3">
-        <f>+AK4*1.01</f>
+      <c r="AQ4" s="3">
+        <f t="shared" ref="AQ4:AW4" si="9">+AP4*1.01</f>
         <v>1574.01688661</v>
       </c>
-      <c r="AM4" s="3">
-        <f>+AL4*1.01</f>
+      <c r="AR4" s="3">
+        <f t="shared" si="9"/>
         <v>1589.7570554761</v>
       </c>
-      <c r="AN4" s="3">
-        <f>+AM4*1.01</f>
+      <c r="AS4" s="3">
+        <f t="shared" si="9"/>
         <v>1605.654626030861</v>
       </c>
-      <c r="AO4" s="3">
-        <f>+AN4*1.01</f>
+      <c r="AT4" s="3">
+        <f t="shared" si="9"/>
         <v>1621.7111722911695</v>
       </c>
-      <c r="AP4" s="3">
-        <f>+AO4*1.01</f>
+      <c r="AU4" s="3">
+        <f t="shared" si="9"/>
         <v>1637.9282840140813</v>
       </c>
-      <c r="AQ4" s="3">
-        <f>+AP4*1.01</f>
+      <c r="AV4" s="3">
+        <f t="shared" si="9"/>
         <v>1654.3075668542222</v>
       </c>
-      <c r="AR4" s="3">
-        <f>+AQ4*1.01</f>
+      <c r="AW4" s="3">
+        <f t="shared" si="9"/>
         <v>1670.8506425227645</v>
       </c>
-      <c r="AS4" s="3">
-        <f>+AR4*0.5</f>
+      <c r="AX4" s="3">
+        <f>+AW4*0.5</f>
         <v>835.42532126138224</v>
       </c>
-      <c r="AT4" s="3">
-        <f>+AS4*0.2</f>
+      <c r="AY4" s="3">
+        <f>+AX4*0.2</f>
         <v>167.08506425227645</v>
       </c>
-      <c r="AU4" s="3">
-        <f t="shared" ref="AU4" si="6">+AT4*0.2</f>
+      <c r="AZ4" s="3">
+        <f t="shared" ref="AZ4" si="10">+AY4*0.2</f>
         <v>33.417012850455293</v>
       </c>
     </row>
-    <row r="5" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
@@ -1896,79 +1981,86 @@
         <v>217.73699999999999</v>
       </c>
       <c r="X5" s="4">
-        <f>+T5*1.07</f>
+        <f t="shared" si="6"/>
         <v>264.39914000000005</v>
       </c>
       <c r="Y5" s="4">
-        <f>+U5*1.07</f>
+        <f t="shared" si="6"/>
         <v>251.53784700000003</v>
       </c>
       <c r="Z5" s="4">
-        <f>+V5*1.07</f>
+        <f t="shared" si="6"/>
         <v>294.30029000000002</v>
       </c>
-      <c r="AG5" s="3">
-        <f t="shared" si="4"/>
+      <c r="AA5" s="4">
+        <v>249.8</v>
+      </c>
+      <c r="AB5" s="4"/>
+      <c r="AC5" s="4"/>
+      <c r="AD5" s="4"/>
+      <c r="AE5" s="4"/>
+      <c r="AL5" s="3">
+        <f t="shared" si="7"/>
         <v>463.64499999999998</v>
       </c>
-      <c r="AH5" s="3">
+      <c r="AM5" s="3">
         <f t="shared" si="1"/>
         <v>736.39799999999991</v>
       </c>
-      <c r="AI5" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN5" s="3">
+        <f t="shared" si="8"/>
         <v>845.46800000000007</v>
       </c>
-      <c r="AJ5" s="3">
-        <f>SUM(S5:V5)</f>
+      <c r="AO5" s="3">
+        <f t="shared" si="2"/>
         <v>955.94710000000009</v>
       </c>
-      <c r="AK5" s="3">
-        <f>SUM(W5:Z5)</f>
+      <c r="AP5" s="3">
+        <f t="shared" si="3"/>
         <v>1027.9742770000003</v>
       </c>
-      <c r="AL5" s="3">
-        <f t="shared" ref="AL5" si="7">+AK5*1.1</f>
+      <c r="AQ5" s="3">
+        <f t="shared" ref="AQ5" si="11">+AP5*1.1</f>
         <v>1130.7717047000003</v>
       </c>
-      <c r="AM5" s="3">
-        <f>+AL5*1.03</f>
+      <c r="AR5" s="3">
+        <f>+AQ5*1.03</f>
         <v>1164.6948558410004</v>
       </c>
-      <c r="AN5" s="3">
-        <f>+AM5*0.7</f>
+      <c r="AS5" s="3">
+        <f>+AR5*0.7</f>
         <v>815.28639908870025</v>
       </c>
-      <c r="AO5" s="3">
-        <f>+AN5*0.7</f>
+      <c r="AT5" s="3">
+        <f>+AS5*0.7</f>
         <v>570.70047936209016</v>
       </c>
-      <c r="AP5" s="3">
-        <f t="shared" ref="AP5:AU5" si="8">+AO5*0.7</f>
+      <c r="AU5" s="3">
+        <f t="shared" ref="AU5:AZ5" si="12">+AT5*0.7</f>
         <v>399.49033555346307</v>
       </c>
-      <c r="AQ5" s="3">
-        <f t="shared" si="8"/>
+      <c r="AV5" s="3">
+        <f t="shared" si="12"/>
         <v>279.64323488742411</v>
       </c>
-      <c r="AR5" s="3">
-        <f t="shared" si="8"/>
+      <c r="AW5" s="3">
+        <f t="shared" si="12"/>
         <v>195.75026442119687</v>
       </c>
-      <c r="AS5" s="3">
-        <f t="shared" si="8"/>
+      <c r="AX5" s="3">
+        <f t="shared" si="12"/>
         <v>137.02518509483781</v>
       </c>
-      <c r="AT5" s="3">
-        <f t="shared" si="8"/>
+      <c r="AY5" s="3">
+        <f t="shared" si="12"/>
         <v>95.917629566386466</v>
       </c>
-      <c r="AU5" s="3">
-        <f t="shared" si="8"/>
+      <c r="AZ5" s="3">
+        <f t="shared" si="12"/>
         <v>67.142340696470526</v>
       </c>
     </row>
-    <row r="6" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
@@ -2042,68 +2134,73 @@
         <f>+V6</f>
         <v>5.173</v>
       </c>
-      <c r="AG6" s="3">
-        <f t="shared" si="4"/>
+      <c r="AA6" s="4"/>
+      <c r="AB6" s="4"/>
+      <c r="AC6" s="4"/>
+      <c r="AD6" s="4"/>
+      <c r="AE6" s="4"/>
+      <c r="AL6" s="3">
+        <f t="shared" si="7"/>
         <v>12.707000000000001</v>
       </c>
-      <c r="AH6" s="3">
+      <c r="AM6" s="3">
         <f t="shared" si="1"/>
         <v>16.825000000000003</v>
       </c>
-      <c r="AI6" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN6" s="3">
+        <f t="shared" si="8"/>
         <v>19.667999999999999</v>
       </c>
-      <c r="AJ6" s="3">
-        <f>SUM(S6:V6)</f>
+      <c r="AO6" s="3">
+        <f t="shared" si="2"/>
         <v>20.673999999999999</v>
       </c>
-      <c r="AK6" s="3">
-        <f>SUM(W6:Z6)</f>
+      <c r="AP6" s="3">
+        <f t="shared" si="3"/>
         <v>23.345999999999997</v>
       </c>
-      <c r="AL6" s="3">
-        <f t="shared" ref="AL6:AU6" si="9">+AK6*0.9</f>
+      <c r="AQ6" s="3">
+        <f t="shared" ref="AQ6:AZ6" si="13">+AP6*0.9</f>
         <v>21.011399999999998</v>
       </c>
-      <c r="AM6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AR6" s="3">
+        <f t="shared" si="13"/>
         <v>18.910259999999997</v>
       </c>
-      <c r="AN6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AS6" s="3">
+        <f t="shared" si="13"/>
         <v>17.019233999999997</v>
       </c>
-      <c r="AO6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AT6" s="3">
+        <f t="shared" si="13"/>
         <v>15.317310599999997</v>
       </c>
-      <c r="AP6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AU6" s="3">
+        <f t="shared" si="13"/>
         <v>13.785579539999997</v>
       </c>
-      <c r="AQ6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AV6" s="3">
+        <f t="shared" si="13"/>
         <v>12.407021585999997</v>
       </c>
-      <c r="AR6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AW6" s="3">
+        <f t="shared" si="13"/>
         <v>11.166319427399998</v>
       </c>
-      <c r="AS6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AX6" s="3">
+        <f t="shared" si="13"/>
         <v>10.049687484659998</v>
       </c>
-      <c r="AT6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AY6" s="3">
+        <f t="shared" si="13"/>
         <v>9.0447187361939978</v>
       </c>
-      <c r="AU6" s="3">
-        <f t="shared" si="9"/>
+      <c r="AZ6" s="3">
+        <f t="shared" si="13"/>
         <v>8.1402468625745978</v>
       </c>
     </row>
-    <row r="7" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
@@ -2135,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="4">
-        <f t="shared" ref="N7" si="10">+M7*0.9</f>
+        <f t="shared" ref="N7" si="14">+M7*0.9</f>
         <v>0</v>
       </c>
       <c r="O7" s="4"/>
@@ -2150,77 +2247,82 @@
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
-      <c r="AD7" s="3">
+      <c r="AA7" s="4"/>
+      <c r="AB7" s="4"/>
+      <c r="AC7" s="4"/>
+      <c r="AD7" s="4"/>
+      <c r="AE7" s="4"/>
+      <c r="AI7" s="3">
         <v>0</v>
       </c>
-      <c r="AE7" s="3">
+      <c r="AJ7" s="3">
         <v>3.714</v>
       </c>
-      <c r="AF7" s="3">
+      <c r="AK7" s="3">
         <v>28.332999999999998</v>
       </c>
-      <c r="AG7" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL7" s="3">
+        <f t="shared" si="7"/>
         <v>57.914000000000001</v>
       </c>
-      <c r="AH7" s="3">
+      <c r="AM7" s="3">
         <f t="shared" si="1"/>
         <v>28.844000000000001</v>
       </c>
-      <c r="AI7" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN7" s="3">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AJ7" s="3">
-        <f>SUM(S7:V7)</f>
+      <c r="AO7" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK7" s="3">
-        <f>SUM(W7:Z7)</f>
+      <c r="AP7" s="3">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AL7" s="3">
-        <f t="shared" ref="AL7:AU7" si="11">+AK7*0.9</f>
+      <c r="AQ7" s="3">
+        <f t="shared" ref="AQ7:AZ7" si="15">+AP7*0.9</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AR7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AN7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AS7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AO7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AT7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AP7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AU7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AQ7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AV7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AR7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AW7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AS7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AX7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AT7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AY7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="AU7" s="3">
-        <f t="shared" si="11"/>
+      <c r="AZ7" s="3">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>25</v>
       </c>
@@ -2294,77 +2396,84 @@
         <f>+V8*1.05</f>
         <v>82.244400000000013</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AA8" s="4">
+        <v>101</v>
+      </c>
+      <c r="AB8" s="4"/>
+      <c r="AC8" s="4"/>
+      <c r="AD8" s="4"/>
+      <c r="AE8" s="4"/>
+      <c r="AI8" s="3">
         <v>0</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AJ8" s="3">
         <v>0</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AK8" s="3">
         <v>90.38</v>
       </c>
-      <c r="AG8" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL8" s="3">
+        <f t="shared" si="7"/>
         <v>246.80799999999999</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AM8" s="3">
         <f t="shared" si="1"/>
         <v>269.91199999999998</v>
       </c>
-      <c r="AI8" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN8" s="3">
+        <f t="shared" si="8"/>
         <v>289.53300000000002</v>
       </c>
-      <c r="AJ8" s="3">
-        <f>SUM(S8:V8)</f>
+      <c r="AO8" s="3">
+        <f t="shared" si="2"/>
         <v>320.26840000000004</v>
       </c>
-      <c r="AK8" s="3">
-        <f>SUM(W8:Z8)</f>
+      <c r="AP8" s="3">
+        <f t="shared" si="3"/>
         <v>320.45982000000004</v>
       </c>
-      <c r="AL8" s="3">
-        <f t="shared" ref="AL8:AU8" si="12">+AK8*1.01</f>
+      <c r="AQ8" s="3">
+        <f t="shared" ref="AQ8:AZ8" si="16">+AP8*1.01</f>
         <v>323.66441820000006</v>
       </c>
-      <c r="AM8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AR8" s="3">
+        <f t="shared" si="16"/>
         <v>326.90106238200008</v>
       </c>
-      <c r="AN8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AS8" s="3">
+        <f t="shared" si="16"/>
         <v>330.17007300582009</v>
       </c>
-      <c r="AO8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AT8" s="3">
+        <f t="shared" si="16"/>
         <v>333.47177373587829</v>
       </c>
-      <c r="AP8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AU8" s="3">
+        <f t="shared" si="16"/>
         <v>336.80649147323709</v>
       </c>
-      <c r="AQ8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AV8" s="3">
+        <f t="shared" si="16"/>
         <v>340.17455638796946</v>
       </c>
-      <c r="AR8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AW8" s="3">
+        <f t="shared" si="16"/>
         <v>343.57630195184913</v>
       </c>
-      <c r="AS8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AX8" s="3">
+        <f t="shared" si="16"/>
         <v>347.01206497136764</v>
       </c>
-      <c r="AT8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AY8" s="3">
+        <f t="shared" si="16"/>
         <v>350.48218562108133</v>
       </c>
-      <c r="AU8" s="3">
-        <f t="shared" si="12"/>
+      <c r="AZ8" s="3">
+        <f t="shared" si="16"/>
         <v>353.98700747729214</v>
       </c>
     </row>
-    <row r="9" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="3" t="s">
         <v>121</v>
       </c>
@@ -2405,56 +2514,63 @@
         <f>+Y9+2</f>
         <v>7.9749999999999996</v>
       </c>
-      <c r="AJ9" s="3">
-        <f>SUM(S9:V9)</f>
+      <c r="AA9" s="4">
+        <v>13.3</v>
+      </c>
+      <c r="AB9" s="4"/>
+      <c r="AC9" s="4"/>
+      <c r="AD9" s="4"/>
+      <c r="AE9" s="4"/>
+      <c r="AO9" s="3">
+        <f t="shared" si="2"/>
         <v>1.0509999999999999</v>
       </c>
-      <c r="AK9" s="3">
-        <f>SUM(W9:Z9)</f>
+      <c r="AP9" s="3">
+        <f t="shared" si="3"/>
         <v>19.899999999999999</v>
       </c>
-      <c r="AL9" s="3">
-        <f>+AK9*1.1</f>
+      <c r="AQ9" s="3">
+        <f t="shared" ref="AQ9:AZ9" si="17">+AP9*1.1</f>
         <v>21.89</v>
       </c>
-      <c r="AM9" s="3">
-        <f>+AL9*1.1</f>
+      <c r="AR9" s="3">
+        <f t="shared" si="17"/>
         <v>24.079000000000004</v>
       </c>
-      <c r="AN9" s="3">
-        <f>+AM9*1.1</f>
+      <c r="AS9" s="3">
+        <f t="shared" si="17"/>
         <v>26.486900000000006</v>
       </c>
-      <c r="AO9" s="3">
-        <f>+AN9*1.1</f>
+      <c r="AT9" s="3">
+        <f t="shared" si="17"/>
         <v>29.135590000000008</v>
       </c>
-      <c r="AP9" s="3">
-        <f>+AO9*1.1</f>
+      <c r="AU9" s="3">
+        <f t="shared" si="17"/>
         <v>32.049149000000014</v>
       </c>
-      <c r="AQ9" s="3">
-        <f>+AP9*1.1</f>
+      <c r="AV9" s="3">
+        <f t="shared" si="17"/>
         <v>35.25406390000002</v>
       </c>
-      <c r="AR9" s="3">
-        <f>+AQ9*1.1</f>
+      <c r="AW9" s="3">
+        <f t="shared" si="17"/>
         <v>38.779470290000027</v>
       </c>
-      <c r="AS9" s="3">
-        <f>+AR9*1.1</f>
+      <c r="AX9" s="3">
+        <f t="shared" si="17"/>
         <v>42.657417319000032</v>
       </c>
-      <c r="AT9" s="3">
-        <f>+AS9*1.1</f>
+      <c r="AY9" s="3">
+        <f t="shared" si="17"/>
         <v>46.92315905090004</v>
       </c>
-      <c r="AU9" s="3">
-        <f>+AT9*1.1</f>
+      <c r="AZ9" s="3">
+        <f t="shared" si="17"/>
         <v>51.615474955990045</v>
       </c>
     </row>
-    <row r="10" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>114</v>
       </c>
@@ -2482,25 +2598,30 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
-      <c r="AD10" s="3">
+      <c r="AA10" s="4"/>
+      <c r="AB10" s="4"/>
+      <c r="AC10" s="4"/>
+      <c r="AD10" s="4"/>
+      <c r="AE10" s="4"/>
+      <c r="AI10" s="3">
         <v>174.739</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AJ10" s="3">
         <v>177.465</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AK10" s="3">
         <v>147.136</v>
       </c>
-      <c r="AJ10" s="3">
-        <f>SUM(S10:V10)</f>
+      <c r="AO10" s="3">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AK10" s="3">
-        <f>SUM(W10:Z10)</f>
+      <c r="AP10" s="3">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>134</v>
       </c>
@@ -2530,42 +2651,49 @@
       <c r="Z11" s="4">
         <v>3</v>
       </c>
-      <c r="AK11" s="3">
-        <f>SUM(W11:Z11)</f>
+      <c r="AA11" s="4">
+        <v>41.4</v>
+      </c>
+      <c r="AB11" s="4"/>
+      <c r="AC11" s="4"/>
+      <c r="AD11" s="4"/>
+      <c r="AE11" s="4"/>
+      <c r="AP11" s="3">
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AQ11" s="3">
         <v>25</v>
       </c>
-      <c r="AM11" s="3">
+      <c r="AR11" s="3">
         <v>50</v>
       </c>
-      <c r="AN11" s="3">
+      <c r="AS11" s="3">
         <v>100</v>
       </c>
-      <c r="AO11" s="3">
+      <c r="AT11" s="3">
         <v>125</v>
       </c>
-      <c r="AP11" s="3">
+      <c r="AU11" s="3">
         <v>150</v>
       </c>
-      <c r="AQ11" s="3">
+      <c r="AV11" s="3">
         <v>175</v>
       </c>
-      <c r="AR11" s="3">
+      <c r="AW11" s="3">
         <v>0</v>
       </c>
-      <c r="AS11" s="3">
+      <c r="AX11" s="3">
         <v>0</v>
       </c>
-      <c r="AT11" s="3">
+      <c r="AY11" s="3">
         <v>0</v>
       </c>
-      <c r="AU11" s="3">
+      <c r="AZ11" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
@@ -2618,7 +2746,7 @@
         <v>107.82899999999999</v>
       </c>
       <c r="U12" s="4">
-        <f t="shared" ref="U12:U15" si="13">+Q12*1.1</f>
+        <f t="shared" ref="U12:U15" si="18">+Q12*1.1</f>
         <v>115.34490000000001</v>
       </c>
       <c r="V12" s="4">
@@ -2639,69 +2767,76 @@
         <f>+V12*1.05</f>
         <v>106.56135</v>
       </c>
-      <c r="AA12" s="4"/>
-      <c r="AG12" s="3">
-        <f t="shared" si="4"/>
+      <c r="AA12" s="4">
+        <v>103.7</v>
+      </c>
+      <c r="AB12" s="4"/>
+      <c r="AC12" s="4"/>
+      <c r="AD12" s="4"/>
+      <c r="AE12" s="4"/>
+      <c r="AF12" s="4"/>
+      <c r="AL12" s="3">
+        <f t="shared" si="7"/>
         <v>85.628999999999991</v>
       </c>
-      <c r="AH12" s="3">
-        <f t="shared" ref="AH12:AH20" si="14">SUM(K12:N12)</f>
+      <c r="AM12" s="3">
+        <f t="shared" ref="AM12:AM20" si="19">SUM(K12:N12)</f>
         <v>281.65899999999999</v>
       </c>
-      <c r="AI12" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN12" s="3">
+        <f t="shared" si="8"/>
         <v>394.226</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AO12" s="3">
         <f>SUM(S12:V12)</f>
         <v>427.41089999999997</v>
       </c>
-      <c r="AK12" s="3">
-        <f>SUM(W12:Z12)</f>
+      <c r="AP12" s="3">
+        <f t="shared" si="3"/>
         <v>435.12694500000003</v>
       </c>
-      <c r="AL12" s="3">
-        <f t="shared" ref="AL12:AU12" si="15">+AK12*1.01</f>
+      <c r="AQ12" s="3">
+        <f t="shared" ref="AQ12:AZ12" si="20">+AP12*1.01</f>
         <v>439.47821445000005</v>
       </c>
-      <c r="AM12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AR12" s="3">
+        <f t="shared" si="20"/>
         <v>443.87299659450008</v>
       </c>
-      <c r="AN12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AS12" s="3">
+        <f t="shared" si="20"/>
         <v>448.31172656044509</v>
       </c>
-      <c r="AO12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AT12" s="3">
+        <f t="shared" si="20"/>
         <v>452.79484382604954</v>
       </c>
-      <c r="AP12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AU12" s="3">
+        <f t="shared" si="20"/>
         <v>457.32279226431007</v>
       </c>
-      <c r="AQ12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AV12" s="3">
+        <f t="shared" si="20"/>
         <v>461.89602018695319</v>
       </c>
-      <c r="AR12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AW12" s="3">
+        <f t="shared" si="20"/>
         <v>466.51498038882272</v>
       </c>
-      <c r="AS12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AX12" s="3">
+        <f t="shared" si="20"/>
         <v>471.18013019271098</v>
       </c>
-      <c r="AT12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AY12" s="3">
+        <f t="shared" si="20"/>
         <v>475.89193149463807</v>
       </c>
-      <c r="AU12" s="3">
-        <f t="shared" si="15"/>
+      <c r="AZ12" s="3">
+        <f t="shared" si="20"/>
         <v>480.65085080958448</v>
       </c>
     </row>
-    <row r="13" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>27</v>
       </c>
@@ -2754,7 +2889,7 @@
         <v>43.012</v>
       </c>
       <c r="U13" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>32.809700000000007</v>
       </c>
       <c r="V13" s="4">
@@ -2764,88 +2899,95 @@
         <v>29.544</v>
       </c>
       <c r="X13" s="4">
-        <f>+T13</f>
+        <f t="shared" ref="X13:Z14" si="21">+T13</f>
         <v>43.012</v>
       </c>
       <c r="Y13" s="4">
-        <f>+U13</f>
+        <f t="shared" si="21"/>
         <v>32.809700000000007</v>
       </c>
       <c r="Z13" s="4">
-        <f>+V13</f>
+        <f t="shared" si="21"/>
         <v>53.247</v>
       </c>
-      <c r="AD13" s="3">
+      <c r="AA13" s="4">
+        <v>26.6</v>
+      </c>
+      <c r="AB13" s="4"/>
+      <c r="AC13" s="4"/>
+      <c r="AD13" s="4"/>
+      <c r="AE13" s="4"/>
+      <c r="AI13" s="3">
         <v>100.83499999999999</v>
       </c>
-      <c r="AE13" s="3">
+      <c r="AJ13" s="3">
         <v>121.407</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AK13" s="3">
         <v>121.105</v>
       </c>
-      <c r="AG13" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL13" s="3">
+        <f t="shared" si="7"/>
         <v>134.06</v>
       </c>
-      <c r="AH13" s="3">
-        <f t="shared" si="14"/>
+      <c r="AM13" s="3">
+        <f t="shared" si="19"/>
         <v>127.97999999999999</v>
       </c>
-      <c r="AI13" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN13" s="3">
+        <f t="shared" si="8"/>
         <v>147.495</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AO13" s="3">
         <f>SUM(S13:V13)</f>
         <v>161.0917</v>
       </c>
-      <c r="AK13" s="3">
-        <f>SUM(W13:Z13)</f>
+      <c r="AP13" s="3">
+        <f t="shared" si="3"/>
         <v>158.61270000000002</v>
       </c>
-      <c r="AL13" s="3">
-        <f t="shared" ref="AL13:AU13" si="16">+AK13*0.99</f>
+      <c r="AQ13" s="3">
+        <f t="shared" ref="AQ13:AZ13" si="22">+AP13*0.99</f>
         <v>157.02657300000001</v>
       </c>
-      <c r="AM13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AR13" s="3">
+        <f t="shared" si="22"/>
         <v>155.45630727000002</v>
       </c>
-      <c r="AN13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AS13" s="3">
+        <f t="shared" si="22"/>
         <v>153.90174419730002</v>
       </c>
-      <c r="AO13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AT13" s="3">
+        <f t="shared" si="22"/>
         <v>152.36272675532703</v>
       </c>
-      <c r="AP13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AU13" s="3">
+        <f t="shared" si="22"/>
         <v>150.83909948777375</v>
       </c>
-      <c r="AQ13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AV13" s="3">
+        <f t="shared" si="22"/>
         <v>149.33070849289601</v>
       </c>
-      <c r="AR13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AW13" s="3">
+        <f t="shared" si="22"/>
         <v>147.83740140796704</v>
       </c>
-      <c r="AS13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AX13" s="3">
+        <f t="shared" si="22"/>
         <v>146.35902739388737</v>
       </c>
-      <c r="AT13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AY13" s="3">
+        <f t="shared" si="22"/>
         <v>144.8954371199485</v>
       </c>
-      <c r="AU13" s="3">
-        <f t="shared" si="16"/>
+      <c r="AZ13" s="3">
+        <f t="shared" si="22"/>
         <v>143.44648274874902</v>
       </c>
     </row>
-    <row r="14" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
         <v>28</v>
       </c>
@@ -2898,7 +3040,7 @@
         <v>45.420999999999999</v>
       </c>
       <c r="U14" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>52.503</v>
       </c>
       <c r="V14" s="4">
@@ -2908,88 +3050,95 @@
         <v>40.661999999999999</v>
       </c>
       <c r="X14" s="4">
-        <f>+T14</f>
+        <f t="shared" si="21"/>
         <v>45.420999999999999</v>
       </c>
       <c r="Y14" s="4">
-        <f>+U14</f>
+        <f t="shared" si="21"/>
         <v>52.503</v>
       </c>
       <c r="Z14" s="4">
-        <f>+V14</f>
+        <f t="shared" si="21"/>
         <v>57.65</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AA14" s="4">
+        <v>47.4</v>
+      </c>
+      <c r="AB14" s="4"/>
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="4"/>
+      <c r="AE14" s="4"/>
+      <c r="AI14" s="3">
         <v>149.44800000000001</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AJ14" s="3">
         <v>172.93799999999999</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AK14" s="3">
         <v>195.84200000000001</v>
       </c>
-      <c r="AG14" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL14" s="3">
+        <f t="shared" si="7"/>
         <v>197.93100000000001</v>
       </c>
-      <c r="AH14" s="3">
-        <f t="shared" si="14"/>
+      <c r="AM14" s="3">
+        <f t="shared" si="19"/>
         <v>194.29</v>
       </c>
-      <c r="AI14" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN14" s="3">
+        <f t="shared" si="8"/>
         <v>184</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AO14" s="3">
         <f>SUM(S14:V14)</f>
         <v>203.25000000000003</v>
       </c>
-      <c r="AK14" s="3">
-        <f>SUM(W14:Z14)</f>
+      <c r="AP14" s="3">
+        <f t="shared" si="3"/>
         <v>196.23600000000002</v>
       </c>
-      <c r="AL14" s="3">
-        <f t="shared" ref="AL14:AU14" si="17">+AK14*0.99</f>
+      <c r="AQ14" s="3">
+        <f t="shared" ref="AQ14:AZ14" si="23">+AP14*0.99</f>
         <v>194.27364000000003</v>
       </c>
-      <c r="AM14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AR14" s="3">
+        <f t="shared" si="23"/>
         <v>192.33090360000003</v>
       </c>
-      <c r="AN14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AS14" s="3">
+        <f t="shared" si="23"/>
         <v>190.40759456400002</v>
       </c>
-      <c r="AO14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AT14" s="3">
+        <f t="shared" si="23"/>
         <v>188.50351861836003</v>
       </c>
-      <c r="AP14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AU14" s="3">
+        <f t="shared" si="23"/>
         <v>186.61848343217642</v>
       </c>
-      <c r="AQ14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AV14" s="3">
+        <f t="shared" si="23"/>
         <v>184.75229859785466</v>
       </c>
-      <c r="AR14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AW14" s="3">
+        <f t="shared" si="23"/>
         <v>182.90477561187612</v>
       </c>
-      <c r="AS14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AX14" s="3">
+        <f t="shared" si="23"/>
         <v>181.07572785575735</v>
       </c>
-      <c r="AT14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AY14" s="3">
+        <f t="shared" si="23"/>
         <v>179.26497057719976</v>
       </c>
-      <c r="AU14" s="3">
-        <f t="shared" si="17"/>
+      <c r="AZ14" s="3">
+        <f t="shared" si="23"/>
         <v>177.47232087142777</v>
       </c>
     </row>
-    <row r="15" spans="1:47" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
@@ -3057,7 +3206,7 @@
         <v>62.378999999999998</v>
       </c>
       <c r="U15" s="4">
-        <f t="shared" si="13"/>
+        <f t="shared" si="18"/>
         <v>40.313900000000004</v>
       </c>
       <c r="V15" s="4">
@@ -3080,80 +3229,88 @@
         <f>+V15*1.03</f>
         <v>67.914080000000013</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AA15" s="4">
+        <f>2.7+36.3+7.3</f>
+        <v>46.3</v>
+      </c>
+      <c r="AB15" s="4"/>
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="4"/>
+      <c r="AE15" s="4"/>
+      <c r="AI15" s="3">
         <f>21.449+39.585</f>
         <v>61.034000000000006</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AJ15" s="3">
         <f>26.16+17.552</f>
         <v>43.712000000000003</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AK15" s="3">
         <f>6.842+16.907</f>
         <v>23.748999999999999</v>
       </c>
-      <c r="AG15" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL15" s="3">
+        <f t="shared" si="7"/>
         <v>94.417000000000002</v>
       </c>
-      <c r="AH15" s="3">
-        <f t="shared" si="14"/>
+      <c r="AM15" s="3">
+        <f t="shared" si="19"/>
         <v>24.588000000000001</v>
       </c>
-      <c r="AI15" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN15" s="3">
+        <f t="shared" si="8"/>
         <v>111.107</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AO15" s="3">
         <f>SUM(S15:V15)</f>
         <v>232.07990000000001</v>
       </c>
-      <c r="AK15" s="3">
-        <f>SUM(W15:Z15)</f>
+      <c r="AP15" s="3">
+        <f t="shared" si="3"/>
         <v>236.89276700000002</v>
       </c>
-      <c r="AL15" s="3">
-        <f t="shared" ref="AL15:AU15" si="18">+AK15*0.99</f>
+      <c r="AQ15" s="3">
+        <f t="shared" ref="AQ15:AZ15" si="24">+AP15*0.99</f>
         <v>234.52383933000002</v>
       </c>
-      <c r="AM15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AR15" s="3">
+        <f t="shared" si="24"/>
         <v>232.17860093670001</v>
       </c>
-      <c r="AN15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AS15" s="3">
+        <f t="shared" si="24"/>
         <v>229.85681492733301</v>
       </c>
-      <c r="AO15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AT15" s="3">
+        <f t="shared" si="24"/>
         <v>227.55824677805967</v>
       </c>
-      <c r="AP15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AU15" s="3">
+        <f t="shared" si="24"/>
         <v>225.28266431027907</v>
       </c>
-      <c r="AQ15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AV15" s="3">
+        <f t="shared" si="24"/>
         <v>223.02983766717628</v>
       </c>
-      <c r="AR15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AW15" s="3">
+        <f t="shared" si="24"/>
         <v>220.79953929050453</v>
       </c>
-      <c r="AS15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AX15" s="3">
+        <f t="shared" si="24"/>
         <v>218.59154389759948</v>
       </c>
-      <c r="AT15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AY15" s="3">
+        <f t="shared" si="24"/>
         <v>216.40562845862348</v>
       </c>
-      <c r="AU15" s="3">
-        <f t="shared" si="18"/>
+      <c r="AZ15" s="3">
+        <f t="shared" si="24"/>
         <v>214.24157217403726</v>
       </c>
     </row>
-    <row r="16" spans="1:47" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:52" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B16" s="5" t="s">
         <v>20</v>
       </c>
@@ -3161,169 +3318,177 @@
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6">
-        <f>SUM(F3:F15)</f>
+        <f t="shared" ref="F16:AA16" si="25">SUM(F3:F15)</f>
         <v>665.51699999999994</v>
       </c>
       <c r="G16" s="6">
-        <f>SUM(G3:G15)</f>
+        <f t="shared" si="25"/>
         <v>607.58100000000002</v>
       </c>
       <c r="H16" s="6">
-        <f>SUM(H3:H15)</f>
+        <f t="shared" si="25"/>
         <v>751.81100000000004</v>
       </c>
       <c r="I16" s="6">
-        <f>SUM(I3:I15)</f>
+        <f t="shared" si="25"/>
         <v>838.11500000000001</v>
       </c>
       <c r="J16" s="6">
-        <f>SUM(J3:J15)</f>
+        <f t="shared" si="25"/>
         <v>896.73099999999999</v>
       </c>
       <c r="K16" s="6">
-        <f>SUM(K3:K15)</f>
+        <f t="shared" si="25"/>
         <v>813.721</v>
       </c>
       <c r="L16" s="6">
-        <f>SUM(L3:L15)</f>
+        <f t="shared" si="25"/>
         <v>932.87800000000004</v>
       </c>
       <c r="M16" s="6">
-        <f>SUM(M3:M15)</f>
+        <f t="shared" si="25"/>
         <v>940.65200000000004</v>
       </c>
       <c r="N16" s="6">
-        <f>SUM(N3:N15)</f>
+        <f t="shared" si="25"/>
         <v>972.12299999999993</v>
       </c>
       <c r="O16" s="6">
-        <f>SUM(O3:O15)</f>
+        <f t="shared" si="25"/>
         <v>892.81200000000001</v>
       </c>
       <c r="P16" s="6">
-        <f>SUM(P3:P15)</f>
+        <f t="shared" si="25"/>
         <v>957.31699999999989</v>
       </c>
       <c r="Q16" s="6">
-        <f>SUM(Q3:Q15)</f>
+        <f t="shared" si="25"/>
         <v>972.14</v>
       </c>
       <c r="R16" s="6">
-        <f>SUM(R3:R15)</f>
+        <f t="shared" si="25"/>
         <v>1011.9349999999999</v>
       </c>
       <c r="S16" s="6">
-        <f>SUM(S3:S15)</f>
+        <f t="shared" si="25"/>
         <v>901.98300000000017</v>
       </c>
       <c r="T16" s="6">
-        <f>SUM(T3:T15)</f>
+        <f t="shared" si="25"/>
         <v>1023.8250000000002</v>
       </c>
       <c r="U16" s="6">
-        <f>SUM(U3:U15)</f>
+        <f t="shared" si="25"/>
         <v>994.20630000000028</v>
       </c>
       <c r="V16" s="6">
-        <f>SUM(V3:V15)</f>
+        <f t="shared" si="25"/>
         <v>1088.173</v>
       </c>
       <c r="W16" s="6">
-        <f>SUM(W3:W15)</f>
+        <f t="shared" si="25"/>
         <v>897.84100000000012</v>
       </c>
       <c r="X16" s="6">
-        <f>SUM(X3:X15)</f>
+        <f t="shared" si="25"/>
         <v>1056.2663500000001</v>
       </c>
       <c r="Y16" s="6">
-        <f>SUM(Y3:Y15)</f>
+        <f t="shared" si="25"/>
         <v>1027.5001200000002</v>
       </c>
       <c r="Z16" s="6">
-        <f>SUM(Z3:Z15)</f>
+        <f t="shared" si="25"/>
         <v>1141.3376000000001</v>
       </c>
-      <c r="AB16" s="6">
+      <c r="AA16" s="6">
+        <f t="shared" si="25"/>
+        <v>1068.7</v>
+      </c>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+      <c r="AG16" s="6">
         <v>1477.261</v>
       </c>
-      <c r="AC16" s="6">
+      <c r="AH16" s="6">
         <v>1601.3989999999999</v>
       </c>
-      <c r="AD16" s="6">
-        <f>SUM(AD3:AD15)</f>
+      <c r="AI16" s="6">
+        <f t="shared" ref="AI16:AZ16" si="26">SUM(AI3:AI15)</f>
         <v>1890.9220000000003</v>
       </c>
-      <c r="AE16" s="6">
-        <f>SUM(AE3:AE15)</f>
+      <c r="AJ16" s="6">
+        <f t="shared" si="26"/>
         <v>2161.761</v>
       </c>
-      <c r="AF16" s="6">
-        <f>SUM(AF3:AF15)</f>
+      <c r="AK16" s="6">
+        <f t="shared" si="26"/>
         <v>2363.567</v>
       </c>
-      <c r="AG16" s="6">
-        <f>SUM(AG3:AG15)</f>
+      <c r="AL16" s="6">
+        <f t="shared" si="26"/>
         <v>3094.2379999999998</v>
       </c>
-      <c r="AH16" s="6">
-        <f>SUM(AH3:AH15)</f>
+      <c r="AM16" s="6">
+        <f t="shared" si="26"/>
         <v>3659.3739999999998</v>
       </c>
-      <c r="AI16" s="6">
-        <f>SUM(AI3:AI15)</f>
+      <c r="AN16" s="6">
+        <f t="shared" si="26"/>
         <v>3834.2040000000002</v>
       </c>
-      <c r="AJ16" s="6">
-        <f>SUM(AJ3:AJ15)</f>
+      <c r="AO16" s="6">
+        <f t="shared" si="26"/>
         <v>4008.1872999999996</v>
       </c>
-      <c r="AK16" s="6">
-        <f>SUM(AK3:AK15)</f>
+      <c r="AP16" s="6">
+        <f t="shared" si="26"/>
         <v>4122.9450700000007</v>
       </c>
-      <c r="AL16" s="6">
-        <f>SUM(AL3:AL15)</f>
+      <c r="AQ16" s="6">
+        <f t="shared" si="26"/>
         <v>4193.1386762900001</v>
       </c>
-      <c r="AM16" s="6">
-        <f>SUM(AM3:AM15)</f>
+      <c r="AR16" s="6">
+        <f t="shared" si="26"/>
         <v>4233.9220421003001</v>
       </c>
-      <c r="AN16" s="6">
-        <f>SUM(AN3:AN15)</f>
+      <c r="AS16" s="6">
+        <f t="shared" si="26"/>
         <v>3934.9656123744594</v>
       </c>
-      <c r="AO16" s="6">
-        <f>SUM(AO3:AO15)</f>
+      <c r="AT16" s="6">
+        <f t="shared" si="26"/>
         <v>3725.4909119669342</v>
       </c>
-      <c r="AP16" s="6">
-        <f>SUM(AP3:AP15)</f>
+      <c r="AU16" s="6">
+        <f t="shared" si="26"/>
         <v>3594.590504075321</v>
       </c>
-      <c r="AQ16" s="6">
-        <f>SUM(AQ3:AQ15)</f>
+      <c r="AV16" s="6">
+        <f t="shared" si="26"/>
         <v>3518.029121060496</v>
       </c>
-      <c r="AR16" s="6">
-        <f>SUM(AR3:AR15)</f>
+      <c r="AW16" s="6">
+        <f t="shared" si="26"/>
         <v>3279.2966015623811</v>
       </c>
-      <c r="AS16" s="6">
-        <f>SUM(AS3:AS15)</f>
+      <c r="AX16" s="6">
+        <f t="shared" si="26"/>
         <v>2389.9345585962028</v>
       </c>
-      <c r="AT16" s="6">
-        <f>SUM(AT3:AT15)</f>
+      <c r="AY16" s="6">
+        <f t="shared" si="26"/>
         <v>1686.1899514397483</v>
       </c>
-      <c r="AU16" s="6">
-        <f>SUM(AU3:AU15)</f>
+      <c r="AZ16" s="6">
+        <f t="shared" si="26"/>
         <v>1530.252922727831</v>
       </c>
     </row>
-    <row r="17" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>30</v>
       </c>
@@ -3397,77 +3562,80 @@
         <f>+Z16-Z18</f>
         <v>114.13375999999994</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AA17" s="3">
+        <v>90</v>
+      </c>
+      <c r="AI17" s="3">
         <v>121.544</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AJ17" s="3">
         <v>127.93</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AK17" s="3">
         <v>148.917</v>
       </c>
-      <c r="AG17" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL17" s="3">
+        <f t="shared" si="7"/>
         <v>205.40100000000001</v>
       </c>
-      <c r="AH17" s="3">
-        <f t="shared" si="14"/>
+      <c r="AM17" s="3">
+        <f t="shared" si="19"/>
         <v>251.94</v>
       </c>
-      <c r="AI17" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN17" s="3">
+        <f t="shared" si="8"/>
         <v>335.65600000000001</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AO17" s="3">
         <f>SUM(S17:V17)</f>
         <v>292.64744099999996</v>
       </c>
-      <c r="AK17" s="3">
-        <f t="shared" ref="AK17:AU17" si="19">+AK16*0.06</f>
+      <c r="AP17" s="3">
+        <f t="shared" ref="AP17:AZ17" si="27">+AP16*0.06</f>
         <v>247.37670420000003</v>
       </c>
-      <c r="AL17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AQ17" s="3">
+        <f t="shared" si="27"/>
         <v>251.5883205774</v>
       </c>
-      <c r="AM17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AR17" s="3">
+        <f t="shared" si="27"/>
         <v>254.03532252601801</v>
       </c>
-      <c r="AN17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AS17" s="3">
+        <f t="shared" si="27"/>
         <v>236.09793674246757</v>
       </c>
-      <c r="AO17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AT17" s="3">
+        <f t="shared" si="27"/>
         <v>223.52945471801604</v>
       </c>
-      <c r="AP17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AU17" s="3">
+        <f t="shared" si="27"/>
         <v>215.67543024451925</v>
       </c>
-      <c r="AQ17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AV17" s="3">
+        <f t="shared" si="27"/>
         <v>211.08174726362975</v>
       </c>
-      <c r="AR17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AW17" s="3">
+        <f t="shared" si="27"/>
         <v>196.75779609374285</v>
       </c>
-      <c r="AS17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AX17" s="3">
+        <f t="shared" si="27"/>
         <v>143.39607351577217</v>
       </c>
-      <c r="AT17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AY17" s="3">
+        <f t="shared" si="27"/>
         <v>101.17139708638489</v>
       </c>
-      <c r="AU17" s="3">
-        <f t="shared" si="19"/>
+      <c r="AZ17" s="3">
+        <f t="shared" si="27"/>
         <v>91.815175363669852</v>
       </c>
     </row>
-    <row r="18" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>31</v>
       </c>
@@ -3475,39 +3643,39 @@
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4">
-        <f t="shared" ref="F18:M18" si="20">+F16-F17</f>
+        <f t="shared" ref="F18:M18" si="28">+F16-F17</f>
         <v>617.21899999999994</v>
       </c>
       <c r="G18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>569.38800000000003</v>
       </c>
       <c r="H18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>701.58500000000004</v>
       </c>
       <c r="I18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>779.24300000000005</v>
       </c>
       <c r="J18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>838.62099999999998</v>
       </c>
       <c r="K18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>765.51499999999999</v>
       </c>
       <c r="L18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>879.63300000000004</v>
       </c>
       <c r="M18" s="4">
-        <f t="shared" si="20"/>
+        <f t="shared" si="28"/>
         <v>883.54900000000009</v>
       </c>
       <c r="N18" s="4">
-        <f t="shared" ref="N18:R18" si="21">+N16-N17</f>
+        <f t="shared" ref="N18:R18" si="29">+N16-N17</f>
         <v>878.73699999999997</v>
       </c>
       <c r="O18" s="4">
@@ -3515,15 +3683,15 @@
         <v>828.08400000000006</v>
       </c>
       <c r="P18" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>859.77999999999986</v>
       </c>
       <c r="Q18" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>869.98699999999997</v>
       </c>
       <c r="R18" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="29"/>
         <v>940.69699999999989</v>
       </c>
       <c r="S18" s="4">
@@ -3558,80 +3726,88 @@
         <f>+Z16*0.9</f>
         <v>1027.2038400000001</v>
       </c>
-      <c r="AD18" s="3">
-        <f t="shared" ref="AD18:AJ18" si="22">+AD16-AD17</f>
+      <c r="AA18" s="4">
+        <f>+AA16-AA17</f>
+        <v>978.7</v>
+      </c>
+      <c r="AB18" s="4"/>
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="4"/>
+      <c r="AE18" s="4"/>
+      <c r="AI18" s="3">
+        <f t="shared" ref="AI18:AN18" si="30">+AI16-AI17</f>
         <v>1769.3780000000002</v>
       </c>
-      <c r="AE18" s="3">
-        <f t="shared" si="22"/>
+      <c r="AJ18" s="3">
+        <f t="shared" si="30"/>
         <v>2033.8309999999999</v>
       </c>
-      <c r="AF18" s="3">
-        <f t="shared" si="22"/>
+      <c r="AK18" s="3">
+        <f t="shared" si="30"/>
         <v>2214.65</v>
       </c>
-      <c r="AG18" s="3">
-        <f t="shared" si="22"/>
+      <c r="AL18" s="3">
+        <f t="shared" si="30"/>
         <v>2888.837</v>
       </c>
-      <c r="AH18" s="3">
-        <f t="shared" si="22"/>
+      <c r="AM18" s="3">
+        <f t="shared" si="30"/>
         <v>3407.4339999999997</v>
       </c>
-      <c r="AI18" s="3">
-        <f t="shared" si="22"/>
+      <c r="AN18" s="3">
+        <f t="shared" si="30"/>
         <v>3498.5480000000002</v>
       </c>
-      <c r="AJ18" s="3">
-        <f>+AJ16-AJ17</f>
+      <c r="AO18" s="3">
+        <f>+AO16-AO17</f>
         <v>3715.5398589999995</v>
       </c>
-      <c r="AK18" s="3">
-        <f t="shared" ref="AK18:AU18" si="23">+AK16-AK17</f>
+      <c r="AP18" s="3">
+        <f t="shared" ref="AP18:AZ18" si="31">+AP16-AP17</f>
         <v>3875.5683658000007</v>
       </c>
-      <c r="AL18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AQ18" s="3">
+        <f t="shared" si="31"/>
         <v>3941.5503557126003</v>
       </c>
-      <c r="AM18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AR18" s="3">
+        <f t="shared" si="31"/>
         <v>3979.8867195742823</v>
       </c>
-      <c r="AN18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AS18" s="3">
+        <f t="shared" si="31"/>
         <v>3698.8676756319919</v>
       </c>
-      <c r="AO18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AT18" s="3">
+        <f t="shared" si="31"/>
         <v>3501.9614572489181</v>
       </c>
-      <c r="AP18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AU18" s="3">
+        <f t="shared" si="31"/>
         <v>3378.9150738308017</v>
       </c>
-      <c r="AQ18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AV18" s="3">
+        <f t="shared" si="31"/>
         <v>3306.947373796866</v>
       </c>
-      <c r="AR18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AW18" s="3">
+        <f t="shared" si="31"/>
         <v>3082.5388054686382</v>
       </c>
-      <c r="AS18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AX18" s="3">
+        <f t="shared" si="31"/>
         <v>2246.5384850804307</v>
       </c>
-      <c r="AT18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AY18" s="3">
+        <f t="shared" si="31"/>
         <v>1585.0185543533635</v>
       </c>
-      <c r="AU18" s="3">
-        <f t="shared" si="23"/>
+      <c r="AZ18" s="3">
+        <f t="shared" si="31"/>
         <v>1438.4377473641612</v>
       </c>
     </row>
-    <row r="19" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>32</v>
       </c>
@@ -3705,77 +3881,84 @@
         <f>+V19</f>
         <v>323.16699999999997</v>
       </c>
-      <c r="AD19" s="3">
+      <c r="AA19" s="4">
+        <v>308.5</v>
+      </c>
+      <c r="AB19" s="4"/>
+      <c r="AC19" s="4"/>
+      <c r="AD19" s="4"/>
+      <c r="AE19" s="4"/>
+      <c r="AI19" s="3">
         <v>683.53</v>
       </c>
-      <c r="AE19" s="3">
+      <c r="AJ19" s="3">
         <v>736.94200000000001</v>
       </c>
-      <c r="AF19" s="3">
+      <c r="AK19" s="3">
         <v>854.23299999999995</v>
       </c>
-      <c r="AG19" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL19" s="3">
+        <f t="shared" si="7"/>
         <v>1105.048</v>
       </c>
-      <c r="AH19" s="3">
-        <f t="shared" si="14"/>
+      <c r="AM19" s="3">
+        <f t="shared" si="19"/>
         <v>1134.704</v>
       </c>
-      <c r="AI19" s="3">
-        <f t="shared" si="5"/>
+      <c r="AN19" s="3">
+        <f t="shared" si="8"/>
         <v>1146.2059999999999</v>
       </c>
-      <c r="AJ19" s="3">
+      <c r="AO19" s="3">
         <f>SUM(S19:V19)</f>
         <v>1246.3519999999999</v>
       </c>
-      <c r="AK19" s="3">
-        <f t="shared" ref="AK19:AU19" si="24">+AK16*0.25</f>
+      <c r="AP19" s="3">
+        <f t="shared" ref="AP19:AZ19" si="32">+AP16*0.25</f>
         <v>1030.7362675000002</v>
       </c>
-      <c r="AL19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AQ19" s="3">
+        <f t="shared" si="32"/>
         <v>1048.2846690725</v>
       </c>
-      <c r="AM19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AR19" s="3">
+        <f t="shared" si="32"/>
         <v>1058.480510525075</v>
       </c>
-      <c r="AN19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AS19" s="3">
+        <f t="shared" si="32"/>
         <v>983.74140309361485</v>
       </c>
-      <c r="AO19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AT19" s="3">
+        <f t="shared" si="32"/>
         <v>931.37272799173354</v>
       </c>
-      <c r="AP19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AU19" s="3">
+        <f t="shared" si="32"/>
         <v>898.64762601883024</v>
       </c>
-      <c r="AQ19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AV19" s="3">
+        <f t="shared" si="32"/>
         <v>879.507280265124</v>
       </c>
-      <c r="AR19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AW19" s="3">
+        <f t="shared" si="32"/>
         <v>819.82415039059526</v>
       </c>
-      <c r="AS19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AX19" s="3">
+        <f t="shared" si="32"/>
         <v>597.4836396490507</v>
       </c>
-      <c r="AT19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AY19" s="3">
+        <f t="shared" si="32"/>
         <v>421.54748785993706</v>
       </c>
-      <c r="AU19" s="3">
-        <f t="shared" si="24"/>
+      <c r="AZ19" s="3">
+        <f t="shared" si="32"/>
         <v>382.56323068195775</v>
       </c>
     </row>
-    <row r="20" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>33</v>
       </c>
@@ -3837,29 +4020,32 @@
       <c r="W20" s="3">
         <v>159.72200000000001</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AA20" s="3">
+        <v>172.3</v>
+      </c>
+      <c r="AI20" s="3">
         <v>226.61600000000001</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AJ20" s="3">
         <v>299.726</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AK20" s="3">
         <v>333.375</v>
       </c>
-      <c r="AG20" s="3">
-        <f t="shared" si="4"/>
+      <c r="AL20" s="3">
+        <f t="shared" si="7"/>
         <v>451.02600000000001</v>
       </c>
-      <c r="AH20" s="3">
-        <f t="shared" si="14"/>
+      <c r="AM20" s="3">
+        <f t="shared" si="19"/>
         <v>521.08500000000004</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AO20" s="3">
         <f>SUM(S20:V20)</f>
         <v>862.73699999999985</v>
       </c>
     </row>
-    <row r="21" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
@@ -3883,43 +4069,43 @@
         <v>403.02200000000005</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" ref="J21:M21" si="25">+J19+J20</f>
+        <f t="shared" ref="J21:M21" si="33">+J19+J20</f>
         <v>468.75700000000001</v>
       </c>
       <c r="K21" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>375.16</v>
       </c>
       <c r="L21" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>405.21199999999999</v>
       </c>
       <c r="M21" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>395.54900000000004</v>
       </c>
       <c r="N21" s="4">
-        <f t="shared" ref="N21" si="26">+N19+N20</f>
+        <f t="shared" ref="N21" si="34">+N19+N20</f>
         <v>479.86799999999994</v>
       </c>
       <c r="O21" s="4">
-        <f t="shared" ref="O21" si="27">+O19+O20</f>
+        <f t="shared" ref="O21" si="35">+O19+O20</f>
         <v>434.43299999999999</v>
       </c>
       <c r="P21" s="4">
-        <f t="shared" ref="P21" si="28">+P19+P20</f>
+        <f t="shared" ref="P21" si="36">+P19+P20</f>
         <v>468.89</v>
       </c>
       <c r="Q21" s="4">
-        <f t="shared" ref="Q21" si="29">+Q19+Q20</f>
+        <f t="shared" ref="Q21" si="37">+Q19+Q20</f>
         <v>542.702</v>
       </c>
       <c r="R21" s="4">
-        <f t="shared" ref="R21:S21" si="30">+R19+R20</f>
+        <f t="shared" ref="R21:S21" si="38">+R19+R20</f>
         <v>501.62699999999995</v>
       </c>
       <c r="S21" s="4">
-        <f t="shared" si="30"/>
+        <f t="shared" si="38"/>
         <v>515.51400000000001</v>
       </c>
       <c r="T21" s="4">
@@ -3927,103 +4113,111 @@
         <v>506.84900000000005</v>
       </c>
       <c r="U21" s="4">
-        <f t="shared" ref="U21:Z21" si="31">+U19+U20</f>
+        <f t="shared" ref="U21:AA21" si="39">+U19+U20</f>
         <v>542.702</v>
       </c>
       <c r="V21" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>544.024</v>
       </c>
       <c r="W21" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>632.06100000000004</v>
       </c>
       <c r="X21" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>303.38600000000002</v>
       </c>
       <c r="Y21" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>308.3</v>
       </c>
       <c r="Z21" s="4">
-        <f t="shared" si="31"/>
+        <f t="shared" si="39"/>
         <v>323.16699999999997</v>
       </c>
-      <c r="AD21" s="3">
-        <f>+AD20+AD19</f>
+      <c r="AA21" s="4">
+        <f t="shared" si="39"/>
+        <v>480.8</v>
+      </c>
+      <c r="AB21" s="4"/>
+      <c r="AC21" s="4"/>
+      <c r="AD21" s="4"/>
+      <c r="AE21" s="4"/>
+      <c r="AI21" s="3">
+        <f>+AI20+AI19</f>
         <v>910.14599999999996</v>
       </c>
-      <c r="AE21" s="3">
-        <f t="shared" ref="AE21:AG21" si="32">+AE20+AE19</f>
+      <c r="AJ21" s="3">
+        <f t="shared" ref="AJ21:AL21" si="40">+AJ20+AJ19</f>
         <v>1036.6680000000001</v>
       </c>
-      <c r="AF21" s="3">
-        <f t="shared" si="32"/>
+      <c r="AK21" s="3">
+        <f t="shared" si="40"/>
         <v>1187.6079999999999</v>
       </c>
-      <c r="AG21" s="3">
-        <f t="shared" si="32"/>
+      <c r="AL21" s="3">
+        <f t="shared" si="40"/>
         <v>1556.0740000000001</v>
       </c>
-      <c r="AH21" s="4">
-        <f t="shared" ref="AH21:AI21" si="33">+AH19+AH20</f>
+      <c r="AM21" s="4">
+        <f t="shared" ref="AM21:AN21" si="41">+AM19+AM20</f>
         <v>1655.789</v>
       </c>
-      <c r="AI21" s="4">
-        <f t="shared" si="33"/>
+      <c r="AN21" s="4">
+        <f t="shared" si="41"/>
         <v>1146.2059999999999</v>
       </c>
-      <c r="AJ21" s="4">
-        <f>+AJ19+AJ20</f>
+      <c r="AO21" s="4">
+        <f>+AO19+AO20</f>
         <v>2109.0889999999999</v>
       </c>
-      <c r="AK21" s="4">
-        <f t="shared" ref="AK21" si="34">+AK19+AK20</f>
+      <c r="AP21" s="4">
+        <f t="shared" ref="AP21" si="42">+AP19+AP20</f>
         <v>1030.7362675000002</v>
       </c>
-      <c r="AL21" s="4">
-        <f t="shared" ref="AL21" si="35">+AL19+AL20</f>
+      <c r="AQ21" s="4">
+        <f t="shared" ref="AQ21" si="43">+AQ19+AQ20</f>
         <v>1048.2846690725</v>
       </c>
-      <c r="AM21" s="4">
-        <f t="shared" ref="AM21" si="36">+AM19+AM20</f>
+      <c r="AR21" s="4">
+        <f t="shared" ref="AR21" si="44">+AR19+AR20</f>
         <v>1058.480510525075</v>
       </c>
-      <c r="AN21" s="4">
-        <f t="shared" ref="AN21" si="37">+AN19+AN20</f>
+      <c r="AS21" s="4">
+        <f t="shared" ref="AS21" si="45">+AS19+AS20</f>
         <v>983.74140309361485</v>
       </c>
-      <c r="AO21" s="4">
-        <f t="shared" ref="AO21" si="38">+AO19+AO20</f>
+      <c r="AT21" s="4">
+        <f t="shared" ref="AT21" si="46">+AT19+AT20</f>
         <v>931.37272799173354</v>
       </c>
-      <c r="AP21" s="4">
-        <f t="shared" ref="AP21" si="39">+AP19+AP20</f>
+      <c r="AU21" s="4">
+        <f t="shared" ref="AU21" si="47">+AU19+AU20</f>
         <v>898.64762601883024</v>
       </c>
-      <c r="AQ21" s="4">
-        <f>+AQ19+AQ20</f>
+      <c r="AV21" s="4">
+        <f>+AV19+AV20</f>
         <v>879.507280265124</v>
       </c>
-      <c r="AR21" s="4">
-        <f t="shared" ref="AR21" si="40">+AR19+AR20</f>
+      <c r="AW21" s="4">
+        <f t="shared" ref="AW21" si="48">+AW19+AW20</f>
         <v>819.82415039059526</v>
       </c>
-      <c r="AS21" s="4">
-        <f t="shared" ref="AS21" si="41">+AS19+AS20</f>
+      <c r="AX21" s="4">
+        <f t="shared" ref="AX21" si="49">+AX19+AX20</f>
         <v>597.4836396490507</v>
       </c>
-      <c r="AT21" s="4">
-        <f t="shared" ref="AT21" si="42">+AT19+AT20</f>
+      <c r="AY21" s="4">
+        <f t="shared" ref="AY21" si="50">+AY19+AY20</f>
         <v>421.54748785993706</v>
       </c>
-      <c r="AU21" s="4">
-        <f t="shared" ref="AU21" si="43">+AU19+AU20</f>
+      <c r="AZ21" s="4">
+        <f t="shared" ref="AZ21" si="51">+AZ19+AZ20</f>
         <v>382.56323068195775</v>
       </c>
     </row>
-    <row r="22" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>35</v>
       </c>
@@ -4047,43 +4241,43 @@
         <v>376.221</v>
       </c>
       <c r="J22" s="4">
-        <f t="shared" ref="J22:M22" si="44">+J18-J21</f>
+        <f t="shared" ref="J22:M22" si="52">+J18-J21</f>
         <v>369.86399999999998</v>
       </c>
       <c r="K22" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>390.35499999999996</v>
       </c>
       <c r="L22" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>474.42100000000005</v>
       </c>
       <c r="M22" s="4">
-        <f t="shared" si="44"/>
+        <f t="shared" si="52"/>
         <v>488.00000000000006</v>
       </c>
       <c r="N22" s="4">
-        <f t="shared" ref="N22" si="45">+N18-N21</f>
+        <f t="shared" ref="N22" si="53">+N18-N21</f>
         <v>398.86900000000003</v>
       </c>
       <c r="O22" s="4">
-        <f t="shared" ref="O22" si="46">+O18-O21</f>
+        <f t="shared" ref="O22" si="54">+O18-O21</f>
         <v>393.65100000000007</v>
       </c>
       <c r="P22" s="4">
-        <f t="shared" ref="P22" si="47">+P18-P21</f>
+        <f t="shared" ref="P22" si="55">+P18-P21</f>
         <v>390.88999999999987</v>
       </c>
       <c r="Q22" s="4">
-        <f t="shared" ref="Q22" si="48">+Q18-Q21</f>
+        <f t="shared" ref="Q22" si="56">+Q18-Q21</f>
         <v>327.28499999999997</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" ref="R22:S22" si="49">+R18-R21</f>
+        <f t="shared" ref="R22:S22" si="57">+R18-R21</f>
         <v>439.06999999999994</v>
       </c>
       <c r="S22" s="4">
-        <f t="shared" si="49"/>
+        <f t="shared" si="57"/>
         <v>322.32100000000014</v>
       </c>
       <c r="T22" s="4">
@@ -4091,103 +4285,111 @@
         <v>444.5630000000001</v>
       </c>
       <c r="U22" s="4">
-        <f t="shared" ref="U22:Z22" si="50">+U18-U21</f>
+        <f t="shared" ref="U22:AA22" si="58">+U18-U21</f>
         <v>381.90985900000032</v>
       </c>
       <c r="V22" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>457.65700000000004</v>
       </c>
       <c r="W22" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>196.08900000000006</v>
       </c>
       <c r="X22" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>647.25371500000006</v>
       </c>
       <c r="Y22" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>616.45010800000023</v>
       </c>
       <c r="Z22" s="4">
-        <f t="shared" si="50"/>
+        <f t="shared" si="58"/>
         <v>704.03684000000021</v>
       </c>
-      <c r="AD22" s="4">
-        <f t="shared" ref="AD22:AF22" si="51">+AD18-AD21</f>
+      <c r="AA22" s="4">
+        <f t="shared" si="58"/>
+        <v>497.90000000000003</v>
+      </c>
+      <c r="AB22" s="4"/>
+      <c r="AC22" s="4"/>
+      <c r="AD22" s="4"/>
+      <c r="AE22" s="4"/>
+      <c r="AI22" s="4">
+        <f t="shared" ref="AI22:AK22" si="59">+AI18-AI21</f>
         <v>859.2320000000002</v>
       </c>
-      <c r="AE22" s="4">
-        <f t="shared" si="51"/>
+      <c r="AJ22" s="4">
+        <f t="shared" si="59"/>
         <v>997.16299999999978</v>
       </c>
-      <c r="AF22" s="4">
-        <f t="shared" si="51"/>
+      <c r="AK22" s="4">
+        <f t="shared" si="59"/>
         <v>1027.0420000000001</v>
       </c>
-      <c r="AG22" s="4">
-        <f t="shared" ref="AG22" si="52">+AG18-AG21</f>
+      <c r="AL22" s="4">
+        <f t="shared" ref="AL22" si="60">+AL18-AL21</f>
         <v>1332.7629999999999</v>
       </c>
-      <c r="AH22" s="4">
-        <f t="shared" ref="AH22:AI22" si="53">+AH18-AH21</f>
+      <c r="AM22" s="4">
+        <f t="shared" ref="AM22:AN22" si="61">+AM18-AM21</f>
         <v>1751.6449999999998</v>
       </c>
-      <c r="AI22" s="4">
-        <f t="shared" si="53"/>
+      <c r="AN22" s="4">
+        <f t="shared" si="61"/>
         <v>2352.3420000000006</v>
       </c>
-      <c r="AJ22" s="4">
-        <f>+AJ18-AJ21</f>
+      <c r="AO22" s="4">
+        <f>+AO18-AO21</f>
         <v>1606.4508589999996</v>
       </c>
-      <c r="AK22" s="4">
-        <f t="shared" ref="AK22" si="54">+AK18-AK21</f>
+      <c r="AP22" s="4">
+        <f t="shared" ref="AP22" si="62">+AP18-AP21</f>
         <v>2844.8320983000003</v>
       </c>
-      <c r="AL22" s="4">
-        <f t="shared" ref="AL22" si="55">+AL18-AL21</f>
+      <c r="AQ22" s="4">
+        <f t="shared" ref="AQ22" si="63">+AQ18-AQ21</f>
         <v>2893.2656866401003</v>
       </c>
-      <c r="AM22" s="4">
-        <f t="shared" ref="AM22" si="56">+AM18-AM21</f>
+      <c r="AR22" s="4">
+        <f t="shared" ref="AR22" si="64">+AR18-AR21</f>
         <v>2921.4062090492071</v>
       </c>
-      <c r="AN22" s="4">
-        <f t="shared" ref="AN22" si="57">+AN18-AN21</f>
+      <c r="AS22" s="4">
+        <f t="shared" ref="AS22" si="65">+AS18-AS21</f>
         <v>2715.1262725383772</v>
       </c>
-      <c r="AO22" s="4">
-        <f t="shared" ref="AO22" si="58">+AO18-AO21</f>
+      <c r="AT22" s="4">
+        <f t="shared" ref="AT22" si="66">+AT18-AT21</f>
         <v>2570.5887292571847</v>
       </c>
-      <c r="AP22" s="4">
-        <f t="shared" ref="AP22" si="59">+AP18-AP21</f>
+      <c r="AU22" s="4">
+        <f t="shared" ref="AU22" si="67">+AU18-AU21</f>
         <v>2480.2674478119716</v>
       </c>
-      <c r="AQ22" s="4">
-        <f>+AQ18-AQ21</f>
+      <c r="AV22" s="4">
+        <f>+AV18-AV21</f>
         <v>2427.4400935317421</v>
       </c>
-      <c r="AR22" s="4">
-        <f t="shared" ref="AR22" si="60">+AR18-AR21</f>
+      <c r="AW22" s="4">
+        <f t="shared" ref="AW22" si="68">+AW18-AW21</f>
         <v>2262.7146550780431</v>
       </c>
-      <c r="AS22" s="4">
-        <f t="shared" ref="AS22" si="61">+AS18-AS21</f>
+      <c r="AX22" s="4">
+        <f t="shared" ref="AX22" si="69">+AX18-AX21</f>
         <v>1649.05484543138</v>
       </c>
-      <c r="AT22" s="4">
-        <f t="shared" ref="AT22" si="62">+AT18-AT21</f>
+      <c r="AY22" s="4">
+        <f t="shared" ref="AY22" si="70">+AY18-AY21</f>
         <v>1163.4710664934264</v>
       </c>
-      <c r="AU22" s="4">
-        <f t="shared" ref="AU22" si="63">+AU18-AU21</f>
+      <c r="AZ22" s="4">
+        <f t="shared" ref="AZ22" si="71">+AZ18-AZ21</f>
         <v>1055.8745166822034</v>
       </c>
     </row>
-    <row r="23" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>36</v>
       </c>
@@ -4261,77 +4463,80 @@
         <f>+Y23</f>
         <v>-53.706000000000003</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AA23" s="3">
+        <v>-39.9</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-78.5</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AJ23" s="3">
         <v>-72.260999999999996</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AK23" s="3">
         <v>-99.706999999999994</v>
       </c>
-      <c r="AG23" s="3">
-        <f t="shared" ref="AG23:AG25" si="64">SUM(G23:J23)</f>
+      <c r="AL23" s="3">
+        <f t="shared" ref="AL23:AL25" si="72">SUM(G23:J23)</f>
         <v>-186.11099999999999</v>
       </c>
-      <c r="AH23" s="3">
-        <f t="shared" ref="AH23:AH25" si="65">SUM(K23:N23)</f>
+      <c r="AM23" s="3">
+        <f t="shared" ref="AM23:AM25" si="73">SUM(K23:N23)</f>
         <v>-256.24</v>
       </c>
-      <c r="AI23" s="3">
-        <f t="shared" ref="AI23:AI25" si="66">SUM(O23:R23)</f>
+      <c r="AN23" s="3">
+        <f t="shared" ref="AN23:AN25" si="74">SUM(O23:R23)</f>
         <v>-289.43800000000005</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AO23" s="3">
         <f>SUM(S23:V23)</f>
         <v>-239.41800000000001</v>
       </c>
-      <c r="AK23" s="3">
-        <f>+AJ37*0.05</f>
+      <c r="AP23" s="3">
+        <f>+AO37*0.05</f>
         <v>0</v>
       </c>
-      <c r="AL23" s="3">
-        <f t="shared" ref="AL23:AU23" si="67">+AK37*$AX$33</f>
+      <c r="AQ23" s="3">
+        <f t="shared" ref="AQ23:AZ23" si="75">+AP37*$BC$33</f>
         <v>-23.391492065999987</v>
       </c>
-      <c r="AM23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AR23" s="3">
+        <f t="shared" si="75"/>
         <v>28.26624343633382</v>
       </c>
-      <c r="AN23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AS23" s="3">
+        <f t="shared" si="75"/>
         <v>81.360347581073555</v>
       </c>
-      <c r="AO23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AT23" s="3">
+        <f t="shared" si="75"/>
         <v>131.69710674322366</v>
       </c>
-      <c r="AP23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AU23" s="3">
+        <f t="shared" si="75"/>
         <v>180.33825179123102</v>
       </c>
-      <c r="AQ23" s="3">
-        <f>+AP37*$AX$33</f>
+      <c r="AV23" s="3">
+        <f>+AU37*$BC$33</f>
         <v>228.22915438408864</v>
       </c>
-      <c r="AR23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AW23" s="3">
+        <f t="shared" si="75"/>
         <v>276.03120084657365</v>
       </c>
-      <c r="AS23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AX23" s="3">
+        <f t="shared" si="75"/>
         <v>321.7286262532167</v>
       </c>
-      <c r="AT23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AY23" s="3">
+        <f t="shared" si="75"/>
         <v>357.20272874353947</v>
       </c>
-      <c r="AU23" s="3">
-        <f t="shared" si="67"/>
+      <c r="AZ23" s="3">
+        <f t="shared" si="75"/>
         <v>384.57485705780482</v>
       </c>
     </row>
-    <row r="24" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>37</v>
       </c>
@@ -4339,31 +4544,31 @@
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4">
-        <f t="shared" ref="F24:L24" si="68">+F22+F23</f>
+        <f t="shared" ref="F24:L24" si="76">+F22+F23</f>
         <v>296.34599999999995</v>
       </c>
       <c r="G24" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>261.37</v>
       </c>
       <c r="H24" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>266.52199999999999</v>
       </c>
       <c r="I24" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>310.89400000000001</v>
       </c>
       <c r="J24" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>307.86599999999999</v>
       </c>
       <c r="K24" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>331.83899999999994</v>
       </c>
       <c r="L24" s="4">
-        <f t="shared" si="68"/>
+        <f t="shared" si="76"/>
         <v>416.80400000000003</v>
       </c>
       <c r="M24" s="4">
@@ -4371,131 +4576,139 @@
         <v>422.01800000000003</v>
       </c>
       <c r="N24" s="4">
-        <f t="shared" ref="N24:Z24" si="69">+N22+N23</f>
+        <f t="shared" ref="N24:AA24" si="77">+N22+N23</f>
         <v>324.74400000000003</v>
       </c>
       <c r="O24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>319.50400000000008</v>
       </c>
       <c r="P24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>317.41999999999985</v>
       </c>
       <c r="Q24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>255.78799999999995</v>
       </c>
       <c r="R24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>368.74599999999992</v>
       </c>
       <c r="S24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>256.20500000000015</v>
       </c>
       <c r="T24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>382.54000000000008</v>
       </c>
       <c r="U24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>321.8868590000003</v>
       </c>
       <c r="V24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>406.40100000000007</v>
       </c>
       <c r="W24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>142.38300000000004</v>
       </c>
       <c r="X24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>593.54771500000004</v>
       </c>
       <c r="Y24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>562.74410800000021</v>
       </c>
       <c r="Z24" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="77"/>
         <v>650.33084000000019</v>
       </c>
-      <c r="AD24" s="4">
-        <f t="shared" ref="AD24:AF24" si="70">+AD22+AD23</f>
+      <c r="AA24" s="4">
+        <f t="shared" si="77"/>
+        <v>458.00000000000006</v>
+      </c>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AI24" s="4">
+        <f t="shared" ref="AI24:AK24" si="78">+AI22+AI23</f>
         <v>780.7320000000002</v>
       </c>
-      <c r="AE24" s="4">
-        <f t="shared" si="70"/>
+      <c r="AJ24" s="4">
+        <f t="shared" si="78"/>
         <v>924.90199999999982</v>
       </c>
-      <c r="AF24" s="4">
-        <f t="shared" si="70"/>
+      <c r="AK24" s="4">
+        <f t="shared" si="78"/>
         <v>927.33500000000015</v>
       </c>
-      <c r="AG24" s="4">
-        <f t="shared" ref="AG24:AI24" si="71">+AG22+AG23</f>
+      <c r="AL24" s="4">
+        <f t="shared" ref="AL24:AN24" si="79">+AL22+AL23</f>
         <v>1146.652</v>
       </c>
-      <c r="AH24" s="4">
-        <f t="shared" si="71"/>
+      <c r="AM24" s="4">
+        <f t="shared" si="79"/>
         <v>1495.4049999999997</v>
       </c>
-      <c r="AI24" s="4">
-        <f t="shared" si="71"/>
+      <c r="AN24" s="4">
+        <f t="shared" si="79"/>
         <v>2062.9040000000005</v>
       </c>
-      <c r="AJ24" s="4">
-        <f>+AJ22+AJ23</f>
+      <c r="AO24" s="4">
+        <f>+AO22+AO23</f>
         <v>1367.0328589999995</v>
       </c>
-      <c r="AK24" s="4">
-        <f t="shared" ref="AK24" si="72">+AK22+AK23</f>
+      <c r="AP24" s="4">
+        <f t="shared" ref="AP24" si="80">+AP22+AP23</f>
         <v>2844.8320983000003</v>
       </c>
-      <c r="AL24" s="4">
-        <f t="shared" ref="AL24" si="73">+AL22+AL23</f>
+      <c r="AQ24" s="4">
+        <f t="shared" ref="AQ24" si="81">+AQ22+AQ23</f>
         <v>2869.8741945741003</v>
       </c>
-      <c r="AM24" s="4">
-        <f t="shared" ref="AM24" si="74">+AM22+AM23</f>
+      <c r="AR24" s="4">
+        <f t="shared" ref="AR24" si="82">+AR22+AR23</f>
         <v>2949.6724524855408</v>
       </c>
-      <c r="AN24" s="4">
-        <f t="shared" ref="AN24" si="75">+AN22+AN23</f>
+      <c r="AS24" s="4">
+        <f t="shared" ref="AS24" si="83">+AS22+AS23</f>
         <v>2796.4866201194509</v>
       </c>
-      <c r="AO24" s="4">
-        <f t="shared" ref="AO24" si="76">+AO22+AO23</f>
+      <c r="AT24" s="4">
+        <f t="shared" ref="AT24" si="84">+AT22+AT23</f>
         <v>2702.2858360004084</v>
       </c>
-      <c r="AP24" s="4">
-        <f t="shared" ref="AP24" si="77">+AP22+AP23</f>
+      <c r="AU24" s="4">
+        <f t="shared" ref="AU24" si="85">+AU22+AU23</f>
         <v>2660.6056996032025</v>
       </c>
-      <c r="AQ24" s="4">
-        <f>+AQ22+AQ23</f>
+      <c r="AV24" s="4">
+        <f>+AV22+AV23</f>
         <v>2655.669247915831</v>
       </c>
-      <c r="AR24" s="4">
-        <f t="shared" ref="AR24" si="78">+AR22+AR23</f>
+      <c r="AW24" s="4">
+        <f t="shared" ref="AW24" si="86">+AW22+AW23</f>
         <v>2538.7458559246165</v>
       </c>
-      <c r="AS24" s="4">
-        <f t="shared" ref="AS24" si="79">+AS22+AS23</f>
+      <c r="AX24" s="4">
+        <f t="shared" ref="AX24" si="87">+AX22+AX23</f>
         <v>1970.7834716845969</v>
       </c>
-      <c r="AT24" s="4">
-        <f t="shared" ref="AT24" si="80">+AT22+AT23</f>
+      <c r="AY24" s="4">
+        <f t="shared" ref="AY24" si="88">+AY22+AY23</f>
         <v>1520.6737952369658</v>
       </c>
-      <c r="AU24" s="4">
-        <f t="shared" ref="AU24" si="81">+AU22+AU23</f>
+      <c r="AZ24" s="4">
+        <f t="shared" ref="AZ24" si="89">+AZ22+AZ23</f>
         <v>1440.4493737400082</v>
       </c>
     </row>
-    <row r="25" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>38</v>
       </c>
@@ -4569,77 +4782,84 @@
         <f>+Z24*0.1</f>
         <v>65.033084000000017</v>
       </c>
-      <c r="AD25" s="3">
+      <c r="AA25" s="4">
+        <v>41.2</v>
+      </c>
+      <c r="AB25" s="4"/>
+      <c r="AC25" s="4"/>
+      <c r="AD25" s="4"/>
+      <c r="AE25" s="4"/>
+      <c r="AI25" s="3">
         <v>80.162000000000006</v>
       </c>
-      <c r="AE25" s="3">
+      <c r="AJ25" s="3">
         <v>-73.153999999999996</v>
       </c>
-      <c r="AF25" s="3">
+      <c r="AK25" s="3">
         <v>33.517000000000003</v>
       </c>
-      <c r="AG25" s="3">
-        <f t="shared" si="64"/>
+      <c r="AL25" s="3">
+        <f t="shared" si="72"/>
         <v>148.76399999999998</v>
       </c>
-      <c r="AH25" s="3">
-        <f t="shared" si="65"/>
+      <c r="AM25" s="3">
+        <f t="shared" si="73"/>
         <v>137.99600000000001</v>
       </c>
-      <c r="AI25" s="3">
-        <f t="shared" si="66"/>
+      <c r="AN25" s="3">
+        <f t="shared" si="74"/>
         <v>144.78500000000003</v>
       </c>
-      <c r="AJ25" s="3">
+      <c r="AO25" s="3">
         <f>SUM(S25:V25)</f>
         <v>120.44368590000002</v>
       </c>
-      <c r="AK25" s="3">
-        <f t="shared" ref="AK25:AU25" si="82">+AK24*0.1</f>
+      <c r="AP25" s="3">
+        <f t="shared" ref="AP25:AZ25" si="90">+AP24*0.1</f>
         <v>284.48320983000002</v>
       </c>
-      <c r="AL25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AQ25" s="3">
+        <f t="shared" si="90"/>
         <v>286.98741945741006</v>
       </c>
-      <c r="AM25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AR25" s="3">
+        <f t="shared" si="90"/>
         <v>294.96724524855409</v>
       </c>
-      <c r="AN25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AS25" s="3">
+        <f t="shared" si="90"/>
         <v>279.64866201194508</v>
       </c>
-      <c r="AO25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AT25" s="3">
+        <f t="shared" si="90"/>
         <v>270.22858360004085</v>
       </c>
-      <c r="AP25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AU25" s="3">
+        <f t="shared" si="90"/>
         <v>266.06056996032027</v>
       </c>
-      <c r="AQ25" s="3">
-        <f>+AQ24*0.1</f>
+      <c r="AV25" s="3">
+        <f>+AV24*0.1</f>
         <v>265.56692479158312</v>
       </c>
-      <c r="AR25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AW25" s="3">
+        <f t="shared" si="90"/>
         <v>253.87458559246167</v>
       </c>
-      <c r="AS25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AX25" s="3">
+        <f t="shared" si="90"/>
         <v>197.07834716845969</v>
       </c>
-      <c r="AT25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AY25" s="3">
+        <f t="shared" si="90"/>
         <v>152.06737952369659</v>
       </c>
-      <c r="AU25" s="3">
-        <f t="shared" si="82"/>
+      <c r="AZ25" s="3">
+        <f t="shared" si="90"/>
         <v>144.04493737400082</v>
       </c>
     </row>
-    <row r="26" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
@@ -4647,31 +4867,31 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4">
-        <f t="shared" ref="F26:L26" si="83">+F24-F25</f>
+        <f t="shared" ref="F26:L26" si="91">+F24-F25</f>
         <v>266.37799999999993</v>
       </c>
       <c r="G26" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="91"/>
         <v>223.71100000000001</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="91"/>
         <v>236.26</v>
       </c>
       <c r="I26" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="91"/>
         <v>267.30500000000001</v>
       </c>
       <c r="J26" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="91"/>
         <v>270.61199999999997</v>
       </c>
       <c r="K26" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="91"/>
         <v>276.61599999999993</v>
       </c>
       <c r="L26" s="4">
-        <f t="shared" si="83"/>
+        <f t="shared" si="91"/>
         <v>378.41700000000003</v>
       </c>
       <c r="M26" s="4">
@@ -4683,540 +4903,556 @@
         <v>324.74400000000003</v>
       </c>
       <c r="O26" s="4">
-        <f t="shared" ref="O26:Z26" si="84">+O24-O25</f>
+        <f t="shared" ref="O26:AA26" si="92">+O24-O25</f>
         <v>279.30700000000007</v>
       </c>
       <c r="P26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>293.09699999999987</v>
       </c>
       <c r="Q26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>208.61199999999997</v>
       </c>
       <c r="R26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>335.65699999999993</v>
       </c>
       <c r="S26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>191.47000000000014</v>
       </c>
       <c r="T26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>359.0200000000001</v>
       </c>
       <c r="U26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>289.69817310000025</v>
       </c>
       <c r="V26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>406.40100000000007</v>
       </c>
       <c r="W26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>105.98900000000003</v>
       </c>
       <c r="X26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>534.19294350000007</v>
       </c>
       <c r="Y26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>506.46969720000016</v>
       </c>
       <c r="Z26" s="4">
-        <f t="shared" si="84"/>
+        <f t="shared" si="92"/>
         <v>585.29775600000016</v>
       </c>
-      <c r="AD26" s="4">
-        <f t="shared" ref="AD26:AF26" si="85">+AD24-AD25</f>
+      <c r="AA26" s="4">
+        <f t="shared" si="92"/>
+        <v>416.80000000000007</v>
+      </c>
+      <c r="AB26" s="4"/>
+      <c r="AC26" s="4"/>
+      <c r="AD26" s="4"/>
+      <c r="AE26" s="4"/>
+      <c r="AI26" s="4">
+        <f t="shared" ref="AI26:AK26" si="93">+AI24-AI25</f>
         <v>700.57000000000016</v>
       </c>
-      <c r="AE26" s="4">
-        <f t="shared" si="85"/>
+      <c r="AJ26" s="4">
+        <f t="shared" si="93"/>
         <v>998.05599999999981</v>
       </c>
-      <c r="AF26" s="4">
-        <f t="shared" si="85"/>
+      <c r="AK26" s="4">
+        <f t="shared" si="93"/>
         <v>893.8180000000001</v>
       </c>
-      <c r="AG26" s="4">
-        <f t="shared" ref="AG26:AJ26" si="86">+AG24-AG25</f>
+      <c r="AL26" s="4">
+        <f t="shared" ref="AL26:AN26" si="94">+AL24-AL25</f>
         <v>997.88800000000003</v>
       </c>
-      <c r="AH26" s="4">
-        <f t="shared" si="86"/>
+      <c r="AM26" s="4">
+        <f t="shared" si="94"/>
         <v>1357.4089999999997</v>
       </c>
-      <c r="AI26" s="4">
-        <f t="shared" si="86"/>
+      <c r="AN26" s="4">
+        <f t="shared" si="94"/>
         <v>1918.1190000000004</v>
       </c>
-      <c r="AJ26" s="4">
-        <f>+AJ24-AJ25</f>
+      <c r="AO26" s="4">
+        <f>+AO24-AO25</f>
         <v>1246.5891730999995</v>
       </c>
-      <c r="AK26" s="4">
-        <f t="shared" ref="AK26" si="87">+AK24-AK25</f>
+      <c r="AP26" s="4">
+        <f t="shared" ref="AP26" si="95">+AP24-AP25</f>
         <v>2560.3488884700005</v>
       </c>
-      <c r="AL26" s="4">
-        <f t="shared" ref="AL26" si="88">+AL24-AL25</f>
+      <c r="AQ26" s="4">
+        <f t="shared" ref="AQ26" si="96">+AQ24-AQ25</f>
         <v>2582.8867751166904</v>
       </c>
-      <c r="AM26" s="4">
-        <f t="shared" ref="AM26" si="89">+AM24-AM25</f>
+      <c r="AR26" s="4">
+        <f t="shared" ref="AR26" si="97">+AR24-AR25</f>
         <v>2654.7052072369866</v>
       </c>
-      <c r="AN26" s="4">
-        <f t="shared" ref="AN26" si="90">+AN24-AN25</f>
+      <c r="AS26" s="4">
+        <f t="shared" ref="AS26" si="98">+AS24-AS25</f>
         <v>2516.837958107506</v>
       </c>
-      <c r="AO26" s="4">
-        <f t="shared" ref="AO26" si="91">+AO24-AO25</f>
+      <c r="AT26" s="4">
+        <f t="shared" ref="AT26" si="99">+AT24-AT25</f>
         <v>2432.0572524003674</v>
       </c>
-      <c r="AP26" s="4">
-        <f t="shared" ref="AP26" si="92">+AP24-AP25</f>
+      <c r="AU26" s="4">
+        <f t="shared" ref="AU26" si="100">+AU24-AU25</f>
         <v>2394.5451296428823</v>
       </c>
-      <c r="AQ26" s="4">
-        <f t="shared" ref="AQ26" si="93">+AQ24-AQ25</f>
+      <c r="AV26" s="4">
+        <f t="shared" ref="AV26" si="101">+AV24-AV25</f>
         <v>2390.102323124248</v>
       </c>
-      <c r="AR26" s="4">
-        <f t="shared" ref="AR26" si="94">+AR24-AR25</f>
+      <c r="AW26" s="4">
+        <f t="shared" ref="AW26" si="102">+AW24-AW25</f>
         <v>2284.8712703321548</v>
       </c>
-      <c r="AS26" s="4">
-        <f t="shared" ref="AS26" si="95">+AS24-AS25</f>
+      <c r="AX26" s="4">
+        <f t="shared" ref="AX26" si="103">+AX24-AX25</f>
         <v>1773.7051245161372</v>
       </c>
-      <c r="AT26" s="4">
-        <f t="shared" ref="AT26" si="96">+AT24-AT25</f>
+      <c r="AY26" s="4">
+        <f t="shared" ref="AY26" si="104">+AY24-AY25</f>
         <v>1368.6064157132691</v>
       </c>
-      <c r="AU26" s="4">
-        <f t="shared" ref="AU26" si="97">+AU24-AU25</f>
+      <c r="AZ26" s="4">
+        <f t="shared" ref="AZ26" si="105">+AZ24-AZ25</f>
         <v>1296.4044363660073</v>
       </c>
-      <c r="AV26" s="3">
-        <f t="shared" ref="AV26:CA26" si="98">+AU26*(1+$AX$32)</f>
+      <c r="BA26" s="3">
+        <f t="shared" ref="BA26:CF26" si="106">+AZ26*(1+$BC$32)</f>
         <v>1231.5842145477068</v>
       </c>
-      <c r="AW26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BB26" s="3">
+        <f t="shared" si="106"/>
         <v>1170.0050038203215</v>
       </c>
-      <c r="AX26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BC26" s="3">
+        <f t="shared" si="106"/>
         <v>1111.5047536293052</v>
       </c>
-      <c r="AY26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BD26" s="3">
+        <f t="shared" si="106"/>
         <v>1055.9295159478399</v>
       </c>
-      <c r="AZ26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BE26" s="3">
+        <f t="shared" si="106"/>
         <v>1003.1330401504479</v>
       </c>
-      <c r="BA26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BF26" s="3">
+        <f t="shared" si="106"/>
         <v>952.97638814292543</v>
       </c>
-      <c r="BB26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BG26" s="3">
+        <f t="shared" si="106"/>
         <v>905.3275687357791</v>
       </c>
-      <c r="BC26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BH26" s="3">
+        <f t="shared" si="106"/>
         <v>860.06119029899014</v>
       </c>
-      <c r="BD26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BI26" s="3">
+        <f t="shared" si="106"/>
         <v>817.0581307840406</v>
       </c>
-      <c r="BE26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BJ26" s="3">
+        <f t="shared" si="106"/>
         <v>776.20522424483852</v>
       </c>
-      <c r="BF26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BK26" s="3">
+        <f t="shared" si="106"/>
         <v>737.39496303259659</v>
       </c>
-      <c r="BG26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BL26" s="3">
+        <f t="shared" si="106"/>
         <v>700.5252148809667</v>
       </c>
-      <c r="BH26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BM26" s="3">
+        <f t="shared" si="106"/>
         <v>665.49895413691831</v>
       </c>
-      <c r="BI26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BN26" s="3">
+        <f t="shared" si="106"/>
         <v>632.22400643007234</v>
       </c>
-      <c r="BJ26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BO26" s="3">
+        <f t="shared" si="106"/>
         <v>600.61280610856875</v>
       </c>
-      <c r="BK26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BP26" s="3">
+        <f t="shared" si="106"/>
         <v>570.58216580314024</v>
       </c>
-      <c r="BL26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BQ26" s="3">
+        <f t="shared" si="106"/>
         <v>542.05305751298317</v>
       </c>
-      <c r="BM26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BR26" s="3">
+        <f t="shared" si="106"/>
         <v>514.95040463733403</v>
       </c>
-      <c r="BN26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BS26" s="3">
+        <f t="shared" si="106"/>
         <v>489.20288440546733</v>
       </c>
-      <c r="BO26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BT26" s="3">
+        <f t="shared" si="106"/>
         <v>464.74274018519395</v>
       </c>
-      <c r="BP26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BU26" s="3">
+        <f t="shared" si="106"/>
         <v>441.50560317593425</v>
       </c>
-      <c r="BQ26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BV26" s="3">
+        <f t="shared" si="106"/>
         <v>419.43032301713754</v>
       </c>
-      <c r="BR26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BW26" s="3">
+        <f t="shared" si="106"/>
         <v>398.45880686628067</v>
       </c>
-      <c r="BS26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BX26" s="3">
+        <f t="shared" si="106"/>
         <v>378.53586652296661</v>
       </c>
-      <c r="BT26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BY26" s="3">
+        <f t="shared" si="106"/>
         <v>359.60907319681826</v>
       </c>
-      <c r="BU26" s="3">
-        <f t="shared" si="98"/>
+      <c r="BZ26" s="3">
+        <f t="shared" si="106"/>
         <v>341.62861953697734</v>
       </c>
-      <c r="BV26" s="3">
-        <f t="shared" si="98"/>
+      <c r="CA26" s="3">
+        <f t="shared" si="106"/>
         <v>324.54718856012846</v>
       </c>
-      <c r="BW26" s="3">
-        <f t="shared" si="98"/>
+      <c r="CB26" s="3">
+        <f t="shared" si="106"/>
         <v>308.31982913212204</v>
       </c>
-      <c r="BX26" s="3">
-        <f t="shared" si="98"/>
+      <c r="CC26" s="3">
+        <f t="shared" si="106"/>
         <v>292.90383767551594</v>
       </c>
-      <c r="BY26" s="3">
-        <f t="shared" si="98"/>
+      <c r="CD26" s="3">
+        <f t="shared" si="106"/>
         <v>278.25864579174015</v>
       </c>
-      <c r="BZ26" s="3">
-        <f t="shared" si="98"/>
+      <c r="CE26" s="3">
+        <f t="shared" si="106"/>
         <v>264.3457135021531</v>
       </c>
-      <c r="CA26" s="3">
-        <f t="shared" si="98"/>
+      <c r="CF26" s="3">
+        <f t="shared" si="106"/>
         <v>251.12842782704544</v>
       </c>
-      <c r="CB26" s="3">
-        <f t="shared" ref="CB26:DF26" si="99">+CA26*(1+$AX$32)</f>
+      <c r="CG26" s="3">
+        <f t="shared" ref="CG26:DK26" si="107">+CF26*(1+$BC$32)</f>
         <v>238.57200643569317</v>
       </c>
-      <c r="CC26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CH26" s="3">
+        <f t="shared" si="107"/>
         <v>226.6434061139085</v>
       </c>
-      <c r="CD26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CI26" s="3">
+        <f t="shared" si="107"/>
         <v>215.31123580821307</v>
       </c>
-      <c r="CE26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CJ26" s="3">
+        <f t="shared" si="107"/>
         <v>204.54567401780241</v>
       </c>
-      <c r="CF26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CK26" s="3">
+        <f t="shared" si="107"/>
         <v>194.31839031691229</v>
       </c>
-      <c r="CG26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CL26" s="3">
+        <f t="shared" si="107"/>
         <v>184.60247080106666</v>
       </c>
-      <c r="CH26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CM26" s="3">
+        <f t="shared" si="107"/>
         <v>175.37234726101332</v>
       </c>
-      <c r="CI26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CN26" s="3">
+        <f t="shared" si="107"/>
         <v>166.60372989796264</v>
       </c>
-      <c r="CJ26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CO26" s="3">
+        <f t="shared" si="107"/>
         <v>158.27354340306451</v>
       </c>
-      <c r="CK26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CP26" s="3">
+        <f t="shared" si="107"/>
         <v>150.35986623291129</v>
       </c>
-      <c r="CL26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CQ26" s="3">
+        <f t="shared" si="107"/>
         <v>142.84187292126572</v>
       </c>
-      <c r="CM26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CR26" s="3">
+        <f t="shared" si="107"/>
         <v>135.69977927520242</v>
       </c>
-      <c r="CN26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CS26" s="3">
+        <f t="shared" si="107"/>
         <v>128.91479031144229</v>
       </c>
-      <c r="CO26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CT26" s="3">
+        <f t="shared" si="107"/>
         <v>122.46905079587017</v>
       </c>
-      <c r="CP26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CU26" s="3">
+        <f t="shared" si="107"/>
         <v>116.34559825607666</v>
       </c>
-      <c r="CQ26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CV26" s="3">
+        <f t="shared" si="107"/>
         <v>110.52831834327282</v>
       </c>
-      <c r="CR26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CW26" s="3">
+        <f t="shared" si="107"/>
         <v>105.00190242610917</v>
       </c>
-      <c r="CS26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CX26" s="3">
+        <f t="shared" si="107"/>
         <v>99.751807304803705</v>
       </c>
-      <c r="CT26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CY26" s="3">
+        <f t="shared" si="107"/>
         <v>94.764216939563511</v>
       </c>
-      <c r="CU26" s="3">
-        <f t="shared" si="99"/>
+      <c r="CZ26" s="3">
+        <f t="shared" si="107"/>
         <v>90.026006092585334</v>
       </c>
-      <c r="CV26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DA26" s="3">
+        <f t="shared" si="107"/>
         <v>85.524705787956066</v>
       </c>
-      <c r="CW26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DB26" s="3">
+        <f t="shared" si="107"/>
         <v>81.248470498558262</v>
       </c>
-      <c r="CX26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DC26" s="3">
+        <f t="shared" si="107"/>
         <v>77.18604697363034</v>
       </c>
-      <c r="CY26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DD26" s="3">
+        <f t="shared" si="107"/>
         <v>73.326744624948816</v>
       </c>
-      <c r="CZ26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DE26" s="3">
+        <f t="shared" si="107"/>
         <v>69.660407393701377</v>
       </c>
-      <c r="DA26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DF26" s="3">
+        <f t="shared" si="107"/>
         <v>66.177387024016298</v>
       </c>
-      <c r="DB26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DG26" s="3">
+        <f t="shared" si="107"/>
         <v>62.868517672815479</v>
       </c>
-      <c r="DC26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DH26" s="3">
+        <f t="shared" si="107"/>
         <v>59.725091789174705</v>
       </c>
-      <c r="DD26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DI26" s="3">
+        <f t="shared" si="107"/>
         <v>56.738837199715967</v>
       </c>
-      <c r="DE26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DJ26" s="3">
+        <f t="shared" si="107"/>
         <v>53.901895339730167</v>
       </c>
-      <c r="DF26" s="3">
-        <f t="shared" si="99"/>
+      <c r="DK26" s="3">
+        <f t="shared" si="107"/>
         <v>51.20680057274366</v>
       </c>
     </row>
-    <row r="27" spans="2:110" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:115" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
         <v>40</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" ref="F27:M27" si="100">+F26/F28</f>
+        <f t="shared" ref="F27:M27" si="108">+F26/F28</f>
         <v>4.6590758036869895</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>3.8311270186494957</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>3.9742295787915487</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>4.3617420533907714</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>4.3999804887566452</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>4.3972212949274319</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>5.9658053633081627</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="108"/>
         <v>6.0146850362347699</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" ref="N27:Z27" si="101">+N26/N28</f>
+        <f t="shared" ref="N27:AA27" si="109">+N26/N28</f>
         <v>5.1504155300386989</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>4.3989510819920001</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>3.9855452814794647</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>2.926121779136801</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>4.8176050981011285</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>3.0617074691782489</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>5.1564811490125688</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>4.1608355202872565</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>6.6078240085849478</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>1.7381229603634043</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>8.7602772019875701</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>8.3056412404270343</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="109"/>
         <v>9.598349530166125</v>
       </c>
-      <c r="AD27" s="20">
-        <f t="shared" ref="AD27:AF27" si="102">+AD26/AD28</f>
+      <c r="AA27" s="9">
+        <f t="shared" si="109"/>
+        <v>6.733441033925688</v>
+      </c>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+      <c r="AI27" s="20">
+        <f t="shared" ref="AI27:AK27" si="110">+AI26/AI28</f>
         <v>11.443295601182603</v>
       </c>
-      <c r="AE27" s="20">
-        <f t="shared" si="102"/>
+      <c r="AJ27" s="20">
+        <f t="shared" si="110"/>
         <v>17.342415291051257</v>
       </c>
-      <c r="AF27" s="20">
-        <f t="shared" si="102"/>
+      <c r="AK27" s="20">
+        <f t="shared" si="110"/>
         <v>15.815029106286605</v>
       </c>
-      <c r="AG27" s="20">
-        <f>+AG26/AG28</f>
+      <c r="AL27" s="20">
+        <f>+AL26/AL28</f>
         <v>16.588061239755973</v>
       </c>
-      <c r="AH27" s="20">
-        <f>+AH26/AH28</f>
+      <c r="AM27" s="20">
+        <f>+AM26/AM28</f>
         <v>21.531222365420835</v>
       </c>
-      <c r="AI27" s="20">
-        <f>+AI26/AI28</f>
+      <c r="AN27" s="20">
+        <f>+AN26/AN28</f>
         <v>27.598834532374106</v>
       </c>
-      <c r="AJ27" s="20">
-        <f>+AJ26/AJ28</f>
+      <c r="AO27" s="20">
+        <f>+AO26/AO28</f>
         <v>18.938648229708676</v>
       </c>
-      <c r="AK27" s="20">
-        <f t="shared" ref="AK27:AU27" si="103">+AK26/AK28</f>
+      <c r="AP27" s="20">
+        <f t="shared" ref="AP27:AZ27" si="111">+AP26/AP28</f>
         <v>38.897776420980669</v>
       </c>
-      <c r="AL27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AQ27" s="20">
+        <f t="shared" si="111"/>
         <v>39.240180411207263</v>
       </c>
-      <c r="AM27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AR27" s="20">
+        <f t="shared" si="111"/>
         <v>40.331272851030974</v>
       </c>
-      <c r="AN27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AS27" s="20">
+        <f t="shared" si="111"/>
         <v>38.236742118690508</v>
       </c>
-      <c r="AO27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AT27" s="20">
+        <f t="shared" si="111"/>
         <v>36.948721978052596</v>
       </c>
-      <c r="AP27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AU27" s="20">
+        <f t="shared" si="111"/>
         <v>36.378823801023692</v>
       </c>
-      <c r="AQ27" s="20">
-        <f>+AQ26/AQ28</f>
+      <c r="AV27" s="20">
+        <f>+AV26/AV28</f>
         <v>36.311327025321852</v>
       </c>
-      <c r="AR27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AW27" s="20">
+        <f t="shared" si="111"/>
         <v>34.712617575026087</v>
       </c>
-      <c r="AS27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AX27" s="20">
+        <f t="shared" si="111"/>
         <v>26.946790603762196</v>
       </c>
-      <c r="AT27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AY27" s="20">
+        <f t="shared" si="111"/>
         <v>20.792379744210095</v>
       </c>
-      <c r="AU27" s="20">
-        <f t="shared" si="103"/>
+      <c r="AZ27" s="20">
+        <f t="shared" si="111"/>
         <v>19.695460311686844</v>
       </c>
     </row>
-    <row r="28" spans="2:110" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:115" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
         <v>1</v>
       </c>
@@ -5290,77 +5526,84 @@
         <f>+Y28</f>
         <v>60.978999999999999</v>
       </c>
-      <c r="AD28" s="3">
+      <c r="AA28" s="4">
+        <v>61.9</v>
+      </c>
+      <c r="AB28" s="4"/>
+      <c r="AC28" s="4"/>
+      <c r="AD28" s="4"/>
+      <c r="AE28" s="4"/>
+      <c r="AI28" s="3">
         <v>61.220999999999997</v>
       </c>
-      <c r="AE28" s="3">
+      <c r="AJ28" s="3">
         <v>57.55</v>
       </c>
-      <c r="AF28" s="3">
+      <c r="AK28" s="3">
         <v>56.517000000000003</v>
       </c>
-      <c r="AG28" s="3">
+      <c r="AL28" s="3">
         <f>AVERAGE(G28:J28)</f>
         <v>60.156999999999996</v>
       </c>
-      <c r="AH28" s="3">
+      <c r="AM28" s="3">
         <f>AVERAGE(K28:N28)</f>
         <v>63.043749999999996</v>
       </c>
-      <c r="AI28" s="3">
+      <c r="AN28" s="3">
         <f>AVERAGE(O28:R28)</f>
         <v>69.5</v>
       </c>
-      <c r="AJ28" s="3">
+      <c r="AO28" s="3">
         <f>AVERAGE(S28:V28)</f>
         <v>65.822500000000005</v>
       </c>
-      <c r="AK28" s="3">
-        <f t="shared" ref="AK28:AU28" si="104">+AJ28</f>
+      <c r="AP28" s="3">
+        <f t="shared" ref="AP28:AZ28" si="112">+AO28</f>
         <v>65.822500000000005</v>
       </c>
-      <c r="AL28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AQ28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AM28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AR28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AN28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AS28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AO28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AT28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AP28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AU28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AQ28" s="3">
-        <f>+AP28</f>
+      <c r="AV28" s="3">
+        <f>+AU28</f>
         <v>65.822500000000005</v>
       </c>
-      <c r="AR28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AW28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AS28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AX28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AT28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AY28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
-      <c r="AU28" s="3">
-        <f t="shared" si="104"/>
+      <c r="AZ28" s="3">
+        <f t="shared" si="112"/>
         <v>65.822500000000005</v>
       </c>
     </row>
-    <row r="29" spans="2:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:115" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C29" s="10"/>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
@@ -5385,8 +5628,13 @@
       <c r="X29" s="10"/>
       <c r="Y29" s="10"/>
       <c r="Z29" s="10"/>
-    </row>
-    <row r="30" spans="2:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="AA29" s="10"/>
+      <c r="AB29" s="10"/>
+      <c r="AC29" s="10"/>
+      <c r="AD29" s="10"/>
+      <c r="AE29" s="10"/>
+    </row>
+    <row r="30" spans="2:115" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>115</v>
       </c>
@@ -5398,51 +5646,51 @@
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
       <c r="J30" s="19">
-        <f t="shared" ref="J30" si="105">+J16/F16-1</f>
+        <f t="shared" ref="J30" si="113">+J16/F16-1</f>
         <v>0.34742012600729977</v>
       </c>
       <c r="K30" s="19">
-        <f t="shared" ref="K30" si="106">+K16/G16-1</f>
+        <f t="shared" ref="K30" si="114">+K16/G16-1</f>
         <v>0.33927986556524981</v>
       </c>
       <c r="L30" s="19">
-        <f t="shared" ref="L30" si="107">+L16/H16-1</f>
+        <f t="shared" ref="L30" si="115">+L16/H16-1</f>
         <v>0.24084111565273725</v>
       </c>
       <c r="M30" s="19">
-        <f t="shared" ref="M30" si="108">+M16/I16-1</f>
+        <f t="shared" ref="M30" si="116">+M16/I16-1</f>
         <v>0.12234239931274349</v>
       </c>
       <c r="N30" s="19">
-        <f t="shared" ref="N30" si="109">+N16/J16-1</f>
+        <f t="shared" ref="N30" si="117">+N16/J16-1</f>
         <v>8.4074265303641704E-2</v>
       </c>
       <c r="O30" s="19">
-        <f t="shared" ref="O30" si="110">+O16/K16-1</f>
+        <f t="shared" ref="O30" si="118">+O16/K16-1</f>
         <v>9.7196705013143259E-2</v>
       </c>
       <c r="P30" s="19">
-        <f t="shared" ref="P30" si="111">+P16/L16-1</f>
+        <f t="shared" ref="P30" si="119">+P16/L16-1</f>
         <v>2.6197423457300806E-2</v>
       </c>
       <c r="Q30" s="19">
-        <f t="shared" ref="Q30" si="112">+Q16/M16-1</f>
+        <f t="shared" ref="Q30" si="120">+Q16/M16-1</f>
         <v>3.3474653750802608E-2</v>
       </c>
       <c r="R30" s="19">
-        <f t="shared" ref="R30" si="113">+R16/N16-1</f>
+        <f t="shared" ref="R30" si="121">+R16/N16-1</f>
         <v>4.0953665328358646E-2</v>
       </c>
       <c r="S30" s="19">
-        <f t="shared" ref="S30:U30" si="114">+S16/O16-1</f>
+        <f t="shared" ref="S30:U30" si="122">+S16/O16-1</f>
         <v>1.027203935430987E-2</v>
       </c>
       <c r="T30" s="19">
-        <f t="shared" si="114"/>
+        <f t="shared" si="122"/>
         <v>6.9473330150828128E-2</v>
       </c>
       <c r="U30" s="19">
-        <f t="shared" si="114"/>
+        <f t="shared" si="122"/>
         <v>2.2698685374534788E-2</v>
       </c>
       <c r="V30" s="19">
@@ -5465,84 +5713,89 @@
         <f>+Z16/V16-1</f>
         <v>4.8856753475780001E-2</v>
       </c>
-      <c r="AC30" s="25">
-        <f>AC16/AB16-1</f>
+      <c r="AA30" s="19"/>
+      <c r="AB30" s="19"/>
+      <c r="AC30" s="19"/>
+      <c r="AD30" s="19"/>
+      <c r="AE30" s="19"/>
+      <c r="AH30" s="24">
+        <f>AH16/AG16-1</f>
         <v>8.4032544012195398E-2</v>
       </c>
-      <c r="AD30" s="25">
-        <f t="shared" ref="AD30:AU30" si="115">AD16/AC16-1</f>
+      <c r="AI30" s="24">
+        <f t="shared" ref="AI30:AZ30" si="123">AI16/AH16-1</f>
         <v>0.18079379342687263</v>
       </c>
-      <c r="AE30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AJ30" s="24">
+        <f t="shared" si="123"/>
         <v>0.14323118563325177</v>
       </c>
-      <c r="AF30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AK30" s="24">
+        <f t="shared" si="123"/>
         <v>9.3352595407170336E-2</v>
       </c>
-      <c r="AG30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AL30" s="24">
+        <f t="shared" si="123"/>
         <v>0.30913911050543508</v>
       </c>
-      <c r="AH30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AM30" s="24">
+        <f t="shared" si="123"/>
         <v>0.18264141284542434</v>
       </c>
-      <c r="AI30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AN30" s="24">
+        <f t="shared" si="123"/>
         <v>4.7775931074550027E-2</v>
       </c>
-      <c r="AJ30" s="25">
-        <f>AJ16/AI16-1</f>
+      <c r="AO30" s="24">
+        <f>AO16/AN16-1</f>
         <v>4.5376641409794471E-2</v>
       </c>
-      <c r="AK30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AP30" s="24">
+        <f t="shared" si="123"/>
         <v>2.8630840180547734E-2</v>
       </c>
-      <c r="AL30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AQ30" s="24">
+        <f t="shared" si="123"/>
         <v>1.7025113140786807E-2</v>
       </c>
-      <c r="AM30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AR30" s="24">
+        <f t="shared" si="123"/>
         <v>9.7262144085308311E-3</v>
       </c>
-      <c r="AN30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AS30" s="24">
+        <f t="shared" si="123"/>
         <v>-7.0609809711455807E-2</v>
       </c>
-      <c r="AO30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AT30" s="24">
+        <f t="shared" si="123"/>
         <v>-5.3234188311272912E-2</v>
       </c>
-      <c r="AP30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AU30" s="24">
+        <f t="shared" si="123"/>
         <v>-3.513641852437166E-2</v>
       </c>
-      <c r="AQ30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AV30" s="24">
+        <f t="shared" si="123"/>
         <v>-2.129905560258516E-2</v>
       </c>
-      <c r="AR30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AW30" s="24">
+        <f t="shared" si="123"/>
         <v>-6.785973375517429E-2</v>
       </c>
-      <c r="AS30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AX30" s="24">
+        <f t="shared" si="123"/>
         <v>-0.27120512445945044</v>
       </c>
-      <c r="AT30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AY30" s="24">
+        <f t="shared" si="123"/>
         <v>-0.29446187328653017</v>
       </c>
-      <c r="AU30" s="25">
-        <f t="shared" si="115"/>
+      <c r="AZ30" s="24">
+        <f t="shared" si="123"/>
         <v>-9.2478921831298355E-2</v>
       </c>
     </row>
-    <row r="31" spans="2:110" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:115" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C31" s="10"/>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
@@ -5567,331 +5820,346 @@
       <c r="X31" s="10"/>
       <c r="Y31" s="10"/>
       <c r="Z31" s="10"/>
-    </row>
-    <row r="32" spans="2:110" x14ac:dyDescent="0.25">
+      <c r="AA31" s="10"/>
+      <c r="AB31" s="10"/>
+      <c r="AC31" s="10"/>
+      <c r="AD31" s="10"/>
+      <c r="AE31" s="10"/>
+    </row>
+    <row r="32" spans="2:115" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>71</v>
       </c>
       <c r="F32" s="19">
-        <f t="shared" ref="F32:T32" si="116">+F18/F16</f>
+        <f t="shared" ref="F32:T32" si="124">+F18/F16</f>
         <v>0.92742784932616296</v>
       </c>
       <c r="G32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.93713924563144668</v>
       </c>
       <c r="H32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.93319331587327137</v>
       </c>
       <c r="I32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.92975665630611559</v>
       </c>
       <c r="J32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.93519795791603055</v>
       </c>
       <c r="K32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.94075856466774233</v>
       </c>
       <c r="L32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.94292394075109498</v>
       </c>
       <c r="M32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.93929423421201474</v>
       </c>
       <c r="N32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.9039360245565633</v>
       </c>
       <c r="O32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.92750097444926816</v>
       </c>
       <c r="P32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.89811420877306047</v>
       </c>
       <c r="Q32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.89491945604542555</v>
       </c>
       <c r="R32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.9296021977696195</v>
       </c>
       <c r="S32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.92888114299271718</v>
       </c>
       <c r="T32" s="19">
-        <f t="shared" si="116"/>
+        <f t="shared" si="124"/>
         <v>0.92927209239860331</v>
       </c>
       <c r="U32" s="19">
-        <f t="shared" ref="U32:Z32" si="117">+U18/U16</f>
+        <f t="shared" ref="U32:Z32" si="125">+U18/U16</f>
         <v>0.93</v>
       </c>
       <c r="V32" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="125"/>
         <v>0.92051631496094832</v>
       </c>
       <c r="W32" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="125"/>
         <v>0.92237935224611034</v>
       </c>
       <c r="X32" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="125"/>
         <v>0.9</v>
       </c>
       <c r="Y32" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="125"/>
         <v>0.9</v>
       </c>
       <c r="Z32" s="19">
-        <f t="shared" si="117"/>
+        <f t="shared" si="125"/>
         <v>0.9</v>
       </c>
-      <c r="AE32" s="19">
-        <f t="shared" ref="AE32:AU32" si="118">+AE18/AE16</f>
+      <c r="AA32" s="19"/>
+      <c r="AB32" s="19"/>
+      <c r="AC32" s="19"/>
+      <c r="AD32" s="19"/>
+      <c r="AE32" s="19"/>
+      <c r="AJ32" s="19">
+        <f t="shared" ref="AJ32:AZ32" si="126">+AJ18/AJ16</f>
         <v>0.9408213951496025</v>
       </c>
-      <c r="AF32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AK32" s="19">
+        <f t="shared" si="126"/>
         <v>0.93699480488600495</v>
       </c>
-      <c r="AG32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AL32" s="19">
+        <f t="shared" si="126"/>
         <v>0.9336182284620641</v>
       </c>
-      <c r="AH32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AM32" s="19">
+        <f t="shared" si="126"/>
         <v>0.93115215881186231</v>
       </c>
-      <c r="AI32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AN32" s="19">
+        <f t="shared" si="126"/>
         <v>0.91245744879510848</v>
       </c>
-      <c r="AJ32" s="19">
-        <f>+AJ18/AJ16</f>
+      <c r="AO32" s="19">
+        <f>+AO18/AO16</f>
         <v>0.9269875833896285</v>
       </c>
-      <c r="AK32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AP32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AL32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AQ32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AM32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AR32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AN32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AS32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AO32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AT32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AP32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AU32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AQ32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AV32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94</v>
       </c>
-      <c r="AR32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AW32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AS32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AX32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AT32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AY32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AU32" s="19">
-        <f t="shared" si="118"/>
+      <c r="AZ32" s="19">
+        <f t="shared" si="126"/>
         <v>0.94000000000000006</v>
       </c>
-      <c r="AW32" s="3" t="s">
+      <c r="BB32" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AX32" s="25">
+      <c r="BC32" s="24">
         <v>-0.05</v>
       </c>
     </row>
-    <row r="33" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="AW33" t="s">
+    <row r="33" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BB33" t="s">
         <v>106</v>
       </c>
-      <c r="AX33" s="25">
+      <c r="BC33" s="24">
         <v>0.02</v>
       </c>
     </row>
-    <row r="34" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>108</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19">
-        <f>SUM(J3:J4)/SUM(F3:F4)-1</f>
+        <f t="shared" ref="J34:Z34" si="127">SUM(J3:J4)/SUM(F3:F4)-1</f>
         <v>3.7157063340153451E-2</v>
       </c>
       <c r="K34" s="19">
-        <f>SUM(K3:K4)/SUM(G3:G4)-1</f>
+        <f t="shared" si="127"/>
         <v>5.5019150002676653E-2</v>
       </c>
       <c r="L34" s="19">
-        <f>SUM(L3:L4)/SUM(H3:H4)-1</f>
+        <f t="shared" si="127"/>
         <v>0.10057903854293482</v>
       </c>
       <c r="M34" s="19">
-        <f>SUM(M3:M4)/SUM(I3:I4)-1</f>
+        <f t="shared" si="127"/>
         <v>0.11203181608875834</v>
       </c>
       <c r="N34" s="19">
-        <f>SUM(N3:N4)/SUM(J3:J4)-1</f>
+        <f t="shared" si="127"/>
         <v>0.12188944442205352</v>
       </c>
       <c r="O34" s="19">
-        <f>SUM(O3:O4)/SUM(K3:K4)-1</f>
+        <f t="shared" si="127"/>
         <v>5.1464907040733365E-2</v>
       </c>
       <c r="P34" s="19">
-        <f>SUM(P3:P4)/SUM(L3:L4)-1</f>
+        <f t="shared" si="127"/>
         <v>-3.590671746827212E-2</v>
       </c>
       <c r="Q34" s="19">
-        <f>SUM(Q3:Q4)/SUM(M3:M4)-1</f>
+        <f t="shared" si="127"/>
         <v>-0.10788026759119107</v>
       </c>
       <c r="R34" s="19">
-        <f>SUM(R3:R4)/SUM(N3:N4)-1</f>
+        <f t="shared" si="127"/>
         <v>-0.160981697171381</v>
       </c>
       <c r="S34" s="19">
-        <f>SUM(S3:S4)/SUM(O3:O4)-1</f>
+        <f t="shared" si="127"/>
         <v>-0.16749398430765239</v>
       </c>
       <c r="T34" s="19">
-        <f>SUM(T3:T4)/SUM(P3:P4)-1</f>
+        <f t="shared" si="127"/>
         <v>-0.11449151096059706</v>
       </c>
       <c r="U34" s="19">
-        <f>SUM(U3:U4)/SUM(Q3:Q4)-1</f>
+        <f t="shared" si="127"/>
         <v>-6.7361076141287279E-2</v>
       </c>
       <c r="V34" s="19">
-        <f>SUM(V3:V4)/SUM(R3:R4)-1</f>
+        <f t="shared" si="127"/>
         <v>1.4679767431378776E-2</v>
       </c>
       <c r="W34" s="19">
-        <f>SUM(W3:W4)/SUM(S3:S4)-1</f>
+        <f t="shared" si="127"/>
         <v>6.6213125638943104E-3</v>
       </c>
       <c r="X34" s="19">
-        <f>SUM(X3:X4)/SUM(T3:T4)-1</f>
+        <f t="shared" si="127"/>
         <v>-3.3892795110668228E-4</v>
       </c>
       <c r="Y34" s="19">
-        <f>SUM(Y3:Y4)/SUM(U3:U4)-1</f>
+        <f t="shared" si="127"/>
         <v>-9.4667003774617786E-4</v>
       </c>
       <c r="Z34" s="19">
-        <f>SUM(Z3:Z4)/SUM(V3:V4)-1</f>
+        <f t="shared" si="127"/>
         <v>2.8913635414677064E-2</v>
       </c>
-      <c r="AH34" s="25">
-        <f>SUM(AH3:AH4)/SUM(AG3:AG4)-1</f>
+      <c r="AA34" s="19"/>
+      <c r="AB34" s="19"/>
+      <c r="AC34" s="19"/>
+      <c r="AD34" s="19"/>
+      <c r="AE34" s="19"/>
+      <c r="AM34" s="24">
+        <f t="shared" ref="AM34:AZ34" si="128">SUM(AM3:AM4)/SUM(AL3:AL4)-1</f>
         <v>9.8688765422982438E-2</v>
       </c>
-      <c r="AI34" s="25">
-        <f>SUM(AI3:AI4)/SUM(AH3:AH4)-1</f>
+      <c r="AN34" s="24">
+        <f t="shared" si="128"/>
         <v>-6.8812225917919134E-2</v>
       </c>
-      <c r="AJ34" s="25">
-        <f>SUM(AJ3:AJ4)/SUM(AI3:AI4)-1</f>
+      <c r="AO34" s="24">
+        <f t="shared" si="128"/>
         <v>-8.4816902524384119E-2</v>
       </c>
-      <c r="AK34" s="25">
-        <f>SUM(AK3:AK4)/SUM(AJ3:AJ4)-1</f>
+      <c r="AP34" s="24">
+        <f t="shared" si="128"/>
         <v>8.884092716718639E-3</v>
       </c>
-      <c r="AL34" s="25">
-        <f>SUM(AL3:AL4)/SUM(AK3:AK4)-1</f>
+      <c r="AQ34" s="24">
+        <f t="shared" si="128"/>
         <v>-3.2853995165680883E-2</v>
       </c>
-      <c r="AM34" s="25">
-        <f>SUM(AM3:AM4)/SUM(AL3:AL4)-1</f>
+      <c r="AR34" s="24">
+        <f t="shared" si="128"/>
         <v>-1.2154873696149981E-2</v>
       </c>
-      <c r="AN34" s="25">
-        <f>SUM(AN3:AN4)/SUM(AM3:AM4)-1</f>
+      <c r="AS34" s="24">
+        <f t="shared" si="128"/>
         <v>-1.2137384222592473E-3</v>
       </c>
-      <c r="AO34" s="25">
-        <f>SUM(AO3:AO4)/SUM(AN3:AN4)-1</f>
+      <c r="AT34" s="24">
+        <f t="shared" si="128"/>
         <v>4.3863172464220224E-3</v>
       </c>
-      <c r="AP34" s="25">
-        <f>SUM(AP3:AP4)/SUM(AO3:AO4)-1</f>
+      <c r="AU34" s="24">
+        <f t="shared" si="128"/>
         <v>7.2054165527821734E-3</v>
       </c>
-      <c r="AQ34" s="25">
-        <f>SUM(AQ3:AQ4)/SUM(AP3:AP4)-1</f>
+      <c r="AV34" s="24">
+        <f t="shared" si="128"/>
         <v>8.6127043196499997E-3</v>
       </c>
-      <c r="AR34" s="25">
-        <f>SUM(AR3:AR4)/SUM(AQ3:AQ4)-1</f>
+      <c r="AW34" s="24">
+        <f t="shared" si="128"/>
         <v>9.3122753290690863E-3</v>
       </c>
-      <c r="AS34" s="25">
-        <f>SUM(AS3:AS4)/SUM(AR3:AR4)-1</f>
+      <c r="AX34" s="24">
+        <f t="shared" si="128"/>
         <v>-0.5</v>
       </c>
-      <c r="AT34" s="25">
-        <f>SUM(AT3:AT4)/SUM(AS3:AS4)-1</f>
+      <c r="AY34" s="24">
+        <f t="shared" si="128"/>
         <v>-0.79979959427128478</v>
       </c>
-      <c r="AU34" s="25">
-        <f>SUM(AU3:AU4)/SUM(AT3:AT4)-1</f>
+      <c r="AZ34" s="24">
+        <f t="shared" si="128"/>
         <v>-0.79949948720636765</v>
       </c>
-      <c r="AW34" s="1" t="s">
+      <c r="BB34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="AX34" s="25">
+      <c r="BC34" s="24">
         <v>0.08</v>
       </c>
     </row>
-    <row r="35" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="AW35" t="s">
+    <row r="35" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BB35" t="s">
         <v>105</v>
       </c>
-      <c r="AX35" s="1">
-        <f>NPV(AX34,AL26:DI26)+Main!K5-Main!K6+AK26</f>
-        <v>19317.213330696683</v>
-      </c>
-    </row>
-    <row r="36" spans="2:50" x14ac:dyDescent="0.25">
-      <c r="AX36" s="20">
-        <f>+AX35/Main!K3</f>
-        <v>313.42402876895909</v>
-      </c>
-    </row>
-    <row r="37" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="BC35" s="1">
+        <f>NPV(BC34,AQ26:DN26)+Main!K5-Main!K6+AP26</f>
+        <v>19612.748330696682</v>
+      </c>
+    </row>
+    <row r="36" spans="2:55" x14ac:dyDescent="0.25">
+      <c r="BC36" s="20">
+        <f>+BC35/Main!K3</f>
+        <v>316.84569193371055</v>
+      </c>
+    </row>
+    <row r="37" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>109</v>
       </c>
@@ -5925,52 +6193,52 @@
         <f>+Y37+Z26</f>
         <v>-1169.5746032999994</v>
       </c>
-      <c r="AK37" s="1">
+      <c r="AP37" s="1">
         <f>+Z37</f>
         <v>-1169.5746032999994</v>
       </c>
-      <c r="AL37" s="1">
-        <f t="shared" ref="AL37:AU37" si="119">+AK37+AL26</f>
+      <c r="AQ37" s="1">
+        <f t="shared" ref="AQ37:AZ37" si="129">+AP37+AQ26</f>
         <v>1413.312171816691</v>
       </c>
-      <c r="AM37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AR37" s="1">
+        <f t="shared" si="129"/>
         <v>4068.0173790536774</v>
       </c>
-      <c r="AN37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AS37" s="1">
+        <f t="shared" si="129"/>
         <v>6584.8553371611833</v>
       </c>
-      <c r="AO37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AT37" s="1">
+        <f t="shared" si="129"/>
         <v>9016.9125895615507</v>
       </c>
-      <c r="AP37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AU37" s="1">
+        <f t="shared" si="129"/>
         <v>11411.457719204433</v>
       </c>
-      <c r="AQ37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AV37" s="1">
+        <f t="shared" si="129"/>
         <v>13801.560042328681</v>
       </c>
-      <c r="AR37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AW37" s="1">
+        <f t="shared" si="129"/>
         <v>16086.431312660836</v>
       </c>
-      <c r="AS37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AX37" s="1">
+        <f t="shared" si="129"/>
         <v>17860.136437176974</v>
       </c>
-      <c r="AT37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AY37" s="1">
+        <f t="shared" si="129"/>
         <v>19228.742852890242</v>
       </c>
-      <c r="AU37" s="1">
-        <f t="shared" si="119"/>
+      <c r="AZ37" s="1">
+        <f t="shared" si="129"/>
         <v>20525.147289256249</v>
       </c>
     </row>
-    <row r="38" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>3</v>
       </c>
@@ -5993,7 +6261,7 @@
         <v>2571.9459999999999</v>
       </c>
     </row>
-    <row r="39" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>122</v>
       </c>
@@ -6015,7 +6283,7 @@
         <v>652.99199999999996</v>
       </c>
     </row>
-    <row r="40" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>123</v>
       </c>
@@ -6037,7 +6305,7 @@
         <v>492.77600000000001</v>
       </c>
     </row>
-    <row r="41" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>129</v>
       </c>
@@ -6059,7 +6327,7 @@
         <v>150.28</v>
       </c>
     </row>
-    <row r="42" spans="2:50" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>130</v>
       </c>
@@ -6081,7 +6349,7 @@
         <v>259.82299999999998</v>
       </c>
     </row>
-    <row r="43" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>131</v>
       </c>
@@ -6089,7 +6357,7 @@
         <v>178.869</v>
       </c>
     </row>
-    <row r="44" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>132</v>
       </c>
@@ -6097,7 +6365,7 @@
         <v>49.180999999999997</v>
       </c>
     </row>
-    <row r="45" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>125</v>
       </c>
@@ -6106,7 +6374,7 @@
         <v>6478.2030000000004</v>
       </c>
     </row>
-    <row r="46" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>126</v>
       </c>
@@ -6114,7 +6382,7 @@
         <v>575.09699999999998</v>
       </c>
     </row>
-    <row r="47" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>127</v>
       </c>
@@ -6122,7 +6390,7 @@
         <v>8.9990000000000006</v>
       </c>
     </row>
-    <row r="48" spans="2:50" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:55" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>128</v>
       </c>
